--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2D8FBE-D115-4825-883E-24BFFFECBFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63049F5D-CC73-46C6-9999-35F28622B721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="2190" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skill!$B$8:$AM$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skill!$B$8:$AP$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="160">
   <si>
     <t>데이터이름</t>
   </si>
@@ -425,122 +425,202 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>PrevCenter</t>
+  </si>
+  <si>
+    <t>NextTriggerTiming</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterEnd</t>
+  </si>
+  <si>
+    <t>트리거로 발동되는 스킬에게는 의미없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 시전했을 때 타겟 방향으로 캐릭터가 회전할지 여부</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>ContactHit</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Obb</t>
+  </si>
+  <si>
+    <t>ElectricShock</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LifetimeMs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적중시 발동스킬Key</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitSkillKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>all</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>client</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastAnim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 애니메이션</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 캐스팅 애니메이션 이름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cast1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectilePrefabPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 이펙트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 이펙트 경로. root 폴더는 Assets/Resources</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>PrevEnd</t>
-  </si>
-  <si>
-    <t>CasterPos</t>
-  </si>
-  <si>
-    <t>PrevCenter</t>
-  </si>
-  <si>
-    <t>NextTriggerTiming</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterEnd</t>
-  </si>
-  <si>
-    <t>트리거로 발동되는 스킬에게는 의미없음</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rotation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 시전했을 때 타겟 방향으로 캐릭터가 회전할지 여부</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Linear</t>
-  </si>
-  <si>
-    <t>ContactHit</t>
-  </si>
-  <si>
-    <t>Static</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Obb</t>
-  </si>
-  <si>
-    <t>ElectricShock</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LifetimeMs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적중시 발동스킬Key</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHitSkillKey</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>all</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>client</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastAnim</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 애니메이션</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 캐스팅 애니메이션 이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cast1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectilePrefabPath</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체 이펙트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체 이펙트 경로. root 폴더는 Assets/Resources</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/Magic circles/Freeze circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/Environment/Teleport</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 이펙트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 이펙트 경로. root 폴더는 Assets/Resources</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectPrefabPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/AoE effects/Red energy explosion</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/Environment/Crystal effect red</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/AoE effects/Meteors AOE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hovl Studio/Magic effects pack/Prefabs/AoE effects/Laser AOE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타게팅 방식</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Targeting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetingMode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nearest</t>
+  </si>
+  <si>
+    <t>HighestGradeNearest</t>
+  </si>
+  <si>
+    <t>Placement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과의 위치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPlacement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forward</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>참고: 다음페이즈 스킬의 경우에는 위치를 NextOrigin이 결정하기 때문에 이 필드를 쓰지않는다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Fireball</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1004,29 +1084,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
     <col min="3" max="4" width="19.25" style="3" customWidth="1"/>
-    <col min="5" max="6" width="21.125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="3" customWidth="1"/>
-    <col min="9" max="10" width="19.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="18.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="23" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.125" style="3" customWidth="1"/>
-    <col min="14" max="15" width="18.25" style="3" customWidth="1"/>
-    <col min="16" max="16" width="20.875" style="3" customWidth="1"/>
-    <col min="17" max="26" width="18.25" style="3" customWidth="1"/>
-    <col min="27" max="27" width="20.75" style="3" customWidth="1"/>
-    <col min="28" max="39" width="18.25" style="3" customWidth="1"/>
-    <col min="40" max="40" width="18.75" style="3" customWidth="1"/>
-    <col min="41" max="16384" width="9" style="3"/>
+    <col min="5" max="5" width="40.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="47.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
+    <col min="10" max="11" width="19.125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="18.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="23" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.125" style="3" customWidth="1"/>
+    <col min="15" max="16" width="18.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="20.875" style="3" customWidth="1"/>
+    <col min="18" max="29" width="18.25" style="3" customWidth="1"/>
+    <col min="30" max="30" width="20.75" style="3" customWidth="1"/>
+    <col min="31" max="42" width="18.25" style="3" customWidth="1"/>
+    <col min="43" max="43" width="18.75" style="3" customWidth="1"/>
+    <col min="44" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1038,8 +1120,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1053,112 +1136,121 @@
         <v>100</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="K2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>79</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>80</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="X2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="AC2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AD2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AE2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AF2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AG2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AH2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AI2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AH2" s="4" t="s">
+      <c r="AK2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AL2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AM2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AP2" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:39" s="7" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1166,42 +1258,46 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="6"/>
+        <v>141</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>132</v>
+      </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="6"/>
+      <c r="N3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="U3" s="6"/>
       <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
+      <c r="W3" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
@@ -1211,23 +1307,26 @@
       <c r="AD3" s="6"/>
       <c r="AE3" s="6"/>
       <c r="AF3" s="6"/>
-      <c r="AG3" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6" t="s">
+      <c r="AJ3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6"/>
+      <c r="AN3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AL3" s="6" t="s">
+      <c r="AO3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AM3" s="6" t="s">
+      <c r="AP3" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1241,13 +1340,13 @@
         <v>101</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>13</v>
@@ -1256,10 +1355,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>13</v>
@@ -1286,11 +1385,11 @@
         <v>13</v>
       </c>
       <c r="T4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="U4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U4" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="V4" s="8" t="s">
         <v>13</v>
       </c>
@@ -1345,8 +1444,17 @@
       <c r="AM4" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="AN4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP4" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1358,55 +1466,55 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="K5" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="S5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="T5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="U5" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="V5" s="8" t="s">
         <v>17</v>
@@ -1415,13 +1523,13 @@
         <v>17</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>16</v>
@@ -1433,22 +1541,22 @@
         <v>16</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="AH5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI5" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="AJ5" s="8" t="s">
         <v>14</v>
@@ -1460,10 +1568,19 @@
         <v>16</v>
       </c>
       <c r="AM5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO5" s="8" t="s">
         <v>16</v>
       </c>
+      <c r="AP5" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1472,40 +1589,44 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="G6" s="8"/>
       <c r="H6" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="8"/>
+      <c r="V6" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="X6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="Y6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
@@ -1519,8 +1640,11 @@
       <c r="AK6" s="8"/>
       <c r="AL6" s="8"/>
       <c r="AM6" s="8"/>
+      <c r="AN6" s="8"/>
+      <c r="AO6" s="8"/>
+      <c r="AP6" s="8"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1531,23 +1655,21 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8" t="b">
         <v>0</v>
       </c>
       <c r="K7" s="8">
         <v>0</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8"/>
       <c r="P7" s="8">
         <v>0</v>
       </c>
@@ -1560,21 +1682,17 @@
       <c r="S7" s="8">
         <v>0</v>
       </c>
-      <c r="T7" s="8" t="b">
+      <c r="T7" s="8">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8">
-        <v>0</v>
-      </c>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
       <c r="AA7" s="8">
         <v>0</v>
       </c>
@@ -1614,8 +1732,17 @@
       <c r="AM7" s="8">
         <v>0</v>
       </c>
+      <c r="AN7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:39" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -1629,112 +1756,121 @@
         <v>102</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>111</v>
-      </c>
       <c r="M8" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="T8" s="10" t="s">
-        <v>114</v>
-      </c>
       <c r="U8" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="X8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="V8" s="10" t="s">
+      <c r="Y8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="AA8" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="AB8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="Z8" s="10" t="s">
+      <c r="AC8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AA8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="AE8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AF8" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AD8" s="10" t="s">
+      <c r="AG8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="AE8" s="10" t="s">
+      <c r="AH8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AF8" s="10" t="s">
+      <c r="AI8" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AG8" s="10" t="s">
+      <c r="AJ8" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AH8" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI8" s="10" t="s">
+      <c r="AK8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AJ8" s="10" t="s">
+      <c r="AM8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AK8" s="10" t="s">
+      <c r="AN8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AL8" s="10" t="s">
+      <c r="AO8" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AM8" s="10" t="s">
+      <c r="AP8" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>1001</v>
       </c>
@@ -1742,165 +1878,179 @@
         <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="3" t="b">
+      <c r="J9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1002</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
+      <c r="M9"/>
+      <c r="O9"/>
       <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
         <v>10</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="T9" s="3" t="b">
+      <c r="U9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U9" t="s">
-        <v>116</v>
-      </c>
       <c r="V9" t="s">
-        <v>117</v>
-      </c>
-      <c r="W9"/>
-      <c r="X9" s="3">
+        <v>150</v>
+      </c>
+      <c r="W9" t="s">
+        <v>155</v>
+      </c>
+      <c r="X9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z9"/>
+      <c r="AA9" s="3">
         <v>50</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
+        <v>8</v>
+      </c>
+      <c r="AF9" s="3">
         <v>20</v>
       </c>
-      <c r="AC9" s="3">
-        <v>30</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>5</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AH9" s="3">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G10" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>112</v>
-      </c>
-      <c r="N10" t="s">
-        <v>108</v>
-      </c>
-      <c r="T10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>118</v>
-      </c>
-      <c r="V10" t="s">
-        <v>119</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="J10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z10" t="s">
         <v>26</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>30</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>1003</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="F11" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="G11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
+      <c r="J11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
         <v>800</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>30</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <v>500</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>800</v>
       </c>
-      <c r="T11" s="3" t="b">
+      <c r="U11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
+        <v>150</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="X11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z11" t="s">
         <v>118</v>
       </c>
-      <c r="V11" t="s">
-        <v>119</v>
-      </c>
-      <c r="W11" t="s">
-        <v>120</v>
-      </c>
-      <c r="X11" s="3">
+      <c r="AA11" s="3">
         <v>15</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AC11" s="3">
         <v>20</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AD11" s="3">
         <v>10</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AI11" s="3">
         <v>500</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AJ11" s="3">
         <v>2000</v>
       </c>
+      <c r="AK11" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>1004</v>
       </c>
@@ -1908,254 +2058,284 @@
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="J12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>1005</v>
       </c>
-      <c r="P12" s="3">
+      <c r="M12" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3" t="b">
+      <c r="U12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="3">
         <v>10</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AM12" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>1005</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="F13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>112</v>
-      </c>
-      <c r="N13" t="s">
-        <v>109</v>
-      </c>
-      <c r="T13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>118</v>
-      </c>
-      <c r="V13" t="s">
-        <v>119</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="J13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z13" t="s">
         <v>26</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AA13" s="3">
         <v>20</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AB13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>1006</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="F14" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1007</v>
       </c>
-      <c r="L14" t="s">
-        <v>112</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="M14" t="s">
+        <v>110</v>
+      </c>
+      <c r="O14" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q14" s="3">
         <v>20000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>80</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3" t="b">
+      <c r="U14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
+        <v>150</v>
+      </c>
+      <c r="W14" t="s">
+        <v>157</v>
+      </c>
+      <c r="X14" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z14" t="s">
         <v>118</v>
       </c>
-      <c r="V14" t="s">
-        <v>119</v>
-      </c>
-      <c r="W14" t="s">
-        <v>120</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="AA14" s="3">
         <v>40</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>5</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
         <v>50</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AK14" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>1007</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>112</v>
-      </c>
-      <c r="N15" t="s">
-        <v>110</v>
-      </c>
-      <c r="T15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
+      <c r="J15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z15" t="s">
         <v>118</v>
       </c>
-      <c r="V15" t="s">
-        <v>119</v>
-      </c>
-      <c r="W15" t="s">
-        <v>120</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="AA15" s="3">
         <v>15</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>5</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>5</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
         <v>50</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AI15" s="3">
         <v>1000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AJ15" s="3">
         <v>1000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AK15" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>1008</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>104</v>
       </c>
-      <c r="I16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16"/>
-      <c r="N16"/>
-      <c r="P16" s="3">
+      <c r="J16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16"/>
+      <c r="O16"/>
+      <c r="Q16" s="3">
         <v>10000</v>
       </c>
-      <c r="T16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" t="s">
-        <v>118</v>
-      </c>
-      <c r="V16" t="s">
-        <v>119</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="U16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="X16" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z16" t="s">
         <v>26</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AA16" s="3">
         <v>30</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AB16" s="3">
         <v>10</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AI16" s="3">
         <v>300</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AJ16" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>1009</v>
       </c>
@@ -2163,153 +2343,171 @@
         <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="J17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
-        <v>500</v>
-      </c>
-      <c r="T17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <v>300</v>
+      </c>
+      <c r="U17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="3">
         <v>5</v>
       </c>
-      <c r="AJ17" s="3">
-        <v>500</v>
-      </c>
     </row>
-    <row r="18" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>1010</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>106</v>
       </c>
+      <c r="F18" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="G18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>1011</v>
       </c>
-      <c r="P18" s="3">
+      <c r="M18" t="s">
+        <v>110</v>
+      </c>
+      <c r="O18" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q18" s="3">
         <v>20000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>80</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1000</v>
       </c>
-      <c r="T18" s="3" t="b">
+      <c r="U18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U18" t="s">
-        <v>118</v>
-      </c>
       <c r="V18" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="W18" t="s">
+        <v>156</v>
+      </c>
+      <c r="X18" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z18" t="s">
         <v>26</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>50</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>10</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AI18" s="3">
         <v>1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AJ18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>1011</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>104</v>
       </c>
-      <c r="I19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>112</v>
-      </c>
-      <c r="N19" t="s">
-        <v>110</v>
-      </c>
-      <c r="T19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" t="s">
-        <v>118</v>
-      </c>
-      <c r="V19" t="s">
-        <v>119</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="J19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z19" t="s">
         <v>26</v>
       </c>
-      <c r="X19" s="3">
+      <c r="AA19" s="3">
         <v>20</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AB19" s="3">
         <v>2</v>
       </c>
-      <c r="AF19" s="3">
+      <c r="AI19" s="3">
         <v>1000</v>
       </c>
-      <c r="AG19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3">
+      <c r="AJ19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="3">
         <v>10</v>
       </c>
-      <c r="AL19" s="3">
+      <c r="AO19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AP19" s="3">
         <v>15</v>
-      </c>
-      <c r="AM19" s="3">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B8:AM9" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B8:AP9" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63049F5D-CC73-46C6-9999-35F28622B721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C343BCC7-3734-411A-9267-2E9730A1EF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="2190" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="2220" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -77,10 +77,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -490,10 +486,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>client</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -621,6 +613,14 @@
   </si>
   <si>
     <t>Prefabs/VFX/Fireball</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1133,121 +1133,121 @@
         <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="T2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AH2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AG2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AK2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AL2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AM2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="AO2" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="AP2" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:42" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
@@ -1258,45 +1258,45 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S3" s="6"/>
       <c r="T3" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V3" s="6"/>
       <c r="W3" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
@@ -1311,19 +1311,19 @@
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
       <c r="AJ3" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK3" s="6"/>
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
       <c r="AN3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="AP3" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
@@ -1337,16 +1337,16 @@
         <v>13</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>13</v>
@@ -1358,7 +1358,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>13</v>
@@ -1388,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V4" s="8" t="s">
         <v>13</v>
@@ -1459,125 +1459,125 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="AB5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AJ5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AK5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AL5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AM5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AN5" s="8" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="AO5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="AP5" s="8" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.3">
@@ -1591,20 +1591,20 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1613,19 +1613,19 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="X6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="Z6" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
@@ -1753,121 +1753,121 @@
         <v>11</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="K8" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="R8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="T8" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="U8" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="X8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="Z8" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="AA8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB8" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="AC8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AD8" s="10" t="s">
+      <c r="AE8" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AE8" s="10" t="s">
+      <c r="AF8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AF8" s="10" t="s">
+      <c r="AG8" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AG8" s="10" t="s">
+      <c r="AH8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="AH8" s="10" t="s">
+      <c r="AI8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AI8" s="10" t="s">
+      <c r="AJ8" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AJ8" s="10" t="s">
+      <c r="AK8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL8" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AK8" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL8" s="10" t="s">
+      <c r="AM8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AM8" s="10" t="s">
+      <c r="AN8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AN8" s="10" t="s">
+      <c r="AO8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AO8" s="10" t="s">
+      <c r="AP8" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="AP8" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.3">
@@ -1875,19 +1875,19 @@
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" t="s">
         <v>103</v>
-      </c>
-      <c r="I9" t="s">
-        <v>104</v>
       </c>
       <c r="J9" s="3" t="b">
         <v>1</v>
@@ -1913,16 +1913,16 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="W9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="X9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" t="s">
         <v>114</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>115</v>
       </c>
       <c r="Z9"/>
       <c r="AA9" s="3">
@@ -1946,31 +1946,31 @@
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z10" t="s">
         <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>26</v>
       </c>
       <c r="AA10" s="3">
         <v>30</v>
@@ -1984,19 +1984,19 @@
         <v>1003</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" t="s">
         <v>103</v>
-      </c>
-      <c r="I11" t="s">
-        <v>104</v>
       </c>
       <c r="J11" s="3" t="b">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X11" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y11" t="s">
         <v>116</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
         <v>117</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>118</v>
       </c>
       <c r="AA11" s="3">
         <v>15</v>
@@ -2055,16 +2055,16 @@
         <v>1004</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="b">
         <v>0</v>
@@ -2073,10 +2073,10 @@
         <v>1005</v>
       </c>
       <c r="M12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="3">
         <v>600</v>
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AA12" s="3">
         <v>0</v>
@@ -2111,17 +2111,17 @@
         <v>1005</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" t="s">
         <v>103</v>
       </c>
-      <c r="I13" t="s">
-        <v>104</v>
-      </c>
       <c r="J13" s="3" t="b">
         <v>0</v>
       </c>
@@ -2129,13 +2129,13 @@
         <v>0</v>
       </c>
       <c r="X13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y13" t="s">
         <v>116</v>
       </c>
-      <c r="Y13" t="s">
-        <v>117</v>
-      </c>
       <c r="Z13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13" s="3">
         <v>20</v>
@@ -2149,19 +2149,19 @@
         <v>1006</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" t="s">
         <v>103</v>
-      </c>
-      <c r="I14" t="s">
-        <v>104</v>
       </c>
       <c r="J14" s="3" t="b">
         <v>0</v>
@@ -2170,10 +2170,10 @@
         <v>1007</v>
       </c>
       <c r="M14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q14" s="3">
         <v>20000</v>
@@ -2191,19 +2191,19 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="W14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="X14" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y14" t="s">
         <v>116</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
         <v>117</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>118</v>
       </c>
       <c r="AA14" s="3">
         <v>40</v>
@@ -2232,17 +2232,17 @@
         <v>1007</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" t="s">
         <v>103</v>
       </c>
-      <c r="I15" t="s">
-        <v>104</v>
-      </c>
       <c r="J15" s="3" t="b">
         <v>0</v>
       </c>
@@ -2250,13 +2250,13 @@
         <v>0</v>
       </c>
       <c r="X15" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y15" t="s">
         <v>116</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Z15" t="s">
         <v>117</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>118</v>
       </c>
       <c r="AA15" s="3">
         <v>15</v>
@@ -2285,19 +2285,19 @@
         <v>1008</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" t="s">
         <v>103</v>
-      </c>
-      <c r="I16" t="s">
-        <v>104</v>
       </c>
       <c r="J16" s="3" t="b">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="X16" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y16" t="s">
         <v>116</v>
       </c>
-      <c r="Y16" t="s">
-        <v>117</v>
-      </c>
       <c r="Z16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA16" s="3">
         <v>30</v>
@@ -2340,16 +2340,16 @@
         <v>1009</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="3" t="b">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AA17" s="3">
         <v>0</v>
@@ -2384,19 +2384,19 @@
         <v>1010</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" t="s">
         <v>103</v>
-      </c>
-      <c r="I18" t="s">
-        <v>104</v>
       </c>
       <c r="J18" s="3" t="b">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         <v>1011</v>
       </c>
       <c r="M18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q18" s="3">
         <v>20000</v>
@@ -2426,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="W18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X18" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y18" t="s">
         <v>116</v>
       </c>
-      <c r="Y18" t="s">
-        <v>117</v>
-      </c>
       <c r="Z18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA18" s="3">
         <v>50</v>
@@ -2458,17 +2458,17 @@
         <v>1011</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" t="s">
         <v>103</v>
       </c>
-      <c r="I19" t="s">
-        <v>104</v>
-      </c>
       <c r="J19" s="3" t="b">
         <v>0</v>
       </c>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="X19" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y19" t="s">
         <v>116</v>
       </c>
-      <c r="Y19" t="s">
-        <v>117</v>
-      </c>
       <c r="Z19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA19" s="3">
         <v>20</v>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C343BCC7-3734-411A-9267-2E9730A1EF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F11D0AB-B513-453B-A7E6-6054823CDA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="2220" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="172">
   <si>
     <t>데이터이름</t>
   </si>
@@ -621,6 +621,54 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Claw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 일반공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Fireball</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 원거리공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stationary</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nearest</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obb</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ContactHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>참고: None 이면 몬스터 스킬임</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/GabrielAguiarProductions/FreeQuickEffectsVol1/Prefabs/vfx_Projectile_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1084,13 +1132,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AP22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
     <col min="3" max="4" width="19.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="63.125" style="3" customWidth="1"/>
     <col min="6" max="6" width="47.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.125" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.25" style="3" customWidth="1"/>
@@ -1266,7 +1314,9 @@
       <c r="G3" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -1877,9 +1927,6 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>131</v>
       </c>
@@ -2504,6 +2551,117 @@
       </c>
       <c r="AP19" s="3">
         <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>9001</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>350</v>
+      </c>
+      <c r="T20" s="3">
+        <v>250</v>
+      </c>
+      <c r="U20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>9002</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>600</v>
+      </c>
+      <c r="T21" s="3">
+        <v>300</v>
+      </c>
+      <c r="U21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>12</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="E22" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F11D0AB-B513-453B-A7E6-6054823CDA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42333183-9F34-4987-8409-17B313784B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="172">
   <si>
     <t>데이터이름</t>
   </si>
@@ -1927,6 +1927,9 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="G9" s="3" t="s">
         <v>131</v>
       </c>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B514C5-9336-4ADD-9730-1C05D0EA7B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDB6797-94AA-430A-8539-C2E13355A61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2293,13 +2293,13 @@
         <v>0</v>
       </c>
       <c r="Y13" s="3">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="Z13" s="3">
         <v>30</v>
       </c>
       <c r="AA13" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" s="3">
         <v>300</v>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDB6797-94AA-430A-8539-C2E13355A61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F944D01-EB7C-4BD1-8DE9-15EC0497DDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="201">
   <si>
     <t>데이터이름</t>
   </si>
@@ -43,6 +43,9 @@
     <t>스킬설명</t>
   </si>
   <si>
+    <t>스킬 아이콘</t>
+  </si>
+  <si>
     <t>Telegraph 이펙트</t>
   </si>
   <si>
@@ -52,6 +55,12 @@
     <t>스킬 이펙트</t>
   </si>
   <si>
+    <t>캐스팅 애니메이션</t>
+  </si>
+  <si>
+    <t>발동 애니메이션</t>
+  </si>
+  <si>
     <t>사운드 이펙트</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
     <t>컬럼설명세부</t>
   </si>
   <si>
+    <t>아이콘</t>
+  </si>
+  <si>
     <t>시전위치표시 이펙트 경로. root 폴더는 Assets/Resources</t>
   </si>
   <si>
@@ -163,6 +175,12 @@
     <t>스킬 이펙트 경로. root 폴더는 Assets/Resources</t>
   </si>
   <si>
+    <t>스킬 캐스팅 애니메이션 이름</t>
+  </si>
+  <si>
+    <t>스킬 발동 애니메이션 이름</t>
+  </si>
+  <si>
     <t>스킬 시전 Sfx. root 폴더는 Assets/Resources</t>
   </si>
   <si>
@@ -193,9 +211,6 @@
     <t>트리거로 발동되는 스킬에게는 의미없음</t>
   </si>
   <si>
-    <t>이 페이즈 동안 캐스터 이동 불가 시간</t>
-  </si>
-  <si>
     <t>스킬 시전했을 때 타겟 방향으로 캐릭터가 회전할지 여부</t>
   </si>
   <si>
@@ -211,9 +226,6 @@
     <t>origin 기준</t>
   </si>
   <si>
-    <t>아이콘</t>
-  </si>
-  <si>
     <t>Target</t>
   </si>
   <si>
@@ -292,6 +304,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Icon</t>
+  </si>
+  <si>
     <t>TelegraphPrefabPath</t>
   </si>
   <si>
@@ -301,6 +316,12 @@
     <t>EffectPrefabPath</t>
   </si>
   <si>
+    <t>CastAnim</t>
+  </si>
+  <si>
+    <t>FireAnim</t>
+  </si>
+  <si>
     <t>SfxCast</t>
   </si>
   <si>
@@ -418,9 +439,6 @@
     <t>ScatterOuterRadius</t>
   </si>
   <si>
-    <t>Icon</t>
-  </si>
-  <si>
     <t>//</t>
   </si>
   <si>
@@ -430,6 +448,12 @@
     <t>Claude/VFX/Sorcerer/Fireball/VS_Sorc_Fireball</t>
   </si>
   <si>
+    <t>Cast_Magic</t>
+  </si>
+  <si>
+    <t>Fire_Magic_1</t>
+  </si>
+  <si>
     <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Cast 4 modified</t>
   </si>
   <si>
@@ -469,12 +493,12 @@
     <t>Circle</t>
   </si>
   <si>
+    <t>Art/SkillIcons/skill_034</t>
+  </si>
+  <si>
     <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fireball_Bullet</t>
   </si>
   <si>
-    <t>Art/SkillIcons/skill_034</t>
-  </si>
-  <si>
     <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fire_CircleShock_modified</t>
   </si>
   <si>
@@ -484,6 +508,9 @@
     <t>Art/Six Elements VFX Mega Pack/FX_Ice Skill/Prefabs/FX_Ice_Crack</t>
   </si>
   <si>
+    <t>Fire_Magic_2</t>
+  </si>
+  <si>
     <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Shoot 5 modified</t>
   </si>
   <si>
@@ -493,129 +520,121 @@
     <t>Obb</t>
   </si>
   <si>
+    <t>Glide</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_051</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>AfterEnd</t>
+  </si>
+  <si>
+    <t>PrevEnd</t>
+  </si>
+  <si>
+    <t>Glide_Shockwave</t>
+  </si>
+  <si>
+    <t>Blaze</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_037</t>
+  </si>
+  <si>
+    <t>PrevCenter</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Blaze_FireField</t>
+  </si>
+  <si>
+    <t>ElectricShock</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_023</t>
+  </si>
+  <si>
+    <t>Teleport</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_191</t>
+  </si>
+  <si>
+    <t>Meteo</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_003</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Floorfire</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Meteor_modified</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Hit 3</t>
+  </si>
+  <si>
+    <t>HighestGradeNearest</t>
+  </si>
+  <si>
+    <t>Meteo_fragment</t>
+  </si>
+  <si>
+    <t>Mob_Claw</t>
+  </si>
+  <si>
+    <t>몬스터 일반공격</t>
+  </si>
+  <si>
+    <t>Mob_Fireball</t>
+  </si>
+  <si>
+    <t>몬스터 원거리공격</t>
+  </si>
+  <si>
+    <t>스킬 시전 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 페이즈 동안 캐스터 이동 불가 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FirePillar</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>불기둥</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Art/SkillIcons/skill_025</t>
-  </si>
-  <si>
-    <t>Glide</t>
-  </si>
-  <si>
-    <t>Mobility</t>
-  </si>
-  <si>
-    <t>AfterEnd</t>
-  </si>
-  <si>
-    <t>PrevEnd</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_051</t>
-  </si>
-  <si>
-    <t>Glide_Shockwave</t>
-  </si>
-  <si>
-    <t>Blaze</t>
-  </si>
-  <si>
-    <t>PrevCenter</t>
-  </si>
-  <si>
-    <t>Forward</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_037</t>
-  </si>
-  <si>
-    <t>Blaze_FireField</t>
-  </si>
-  <si>
-    <t>ElectricShock</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_023</t>
-  </si>
-  <si>
-    <t>Teleport</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_191</t>
-  </si>
-  <si>
-    <t>Meteo</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Floorfire</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Meteor_modified</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_140</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_0104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Pure Flames</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Hit 3</t>
-  </si>
-  <si>
-    <t>HighestGradeNearest</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_003</t>
-  </si>
-  <si>
-    <t>Meteo_fragment</t>
-  </si>
-  <si>
-    <t>Mob_Claw</t>
-  </si>
-  <si>
-    <t>몬스터 일반공격</t>
-  </si>
-  <si>
-    <t>Mob_Fireball</t>
-  </si>
-  <si>
-    <t>몬스터 원거리공격</t>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Fireball</t>
-  </si>
-  <si>
-    <t>스킬 아이콘</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Fire_Magic_1</t>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Fire_Magic_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 캐스팅 애니메이션 이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>발동 애니메이션</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 애니메이션</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastAnim</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cast_Magic</t>
-  </si>
-  <si>
-    <t>스킬 발동 애니메이션 이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FireAnim</t>
+    <t>Art/GabrielAguiarProductions_Projectile/UniqueProjectilesVol_4/Prefabs/Projectiles/vfx_Projectile_Arrow06</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1086,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1095,7 +1114,7 @@
     <col min="5" max="5" width="22" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="63.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="47.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="73.75" style="3" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="3" customWidth="1"/>
     <col min="10" max="14" width="21.125" style="3" customWidth="1"/>
     <col min="15" max="15" width="24.125" style="3" customWidth="1"/>
@@ -1110,8 +1129,8 @@
     <col min="26" max="37" width="18.25" style="3" customWidth="1"/>
     <col min="38" max="38" width="20.75" style="3" customWidth="1"/>
     <col min="39" max="50" width="18.25" style="3" customWidth="1"/>
-    <col min="51" max="51" width="9" style="3" customWidth="1"/>
-    <col min="52" max="16384" width="9" style="3"/>
+    <col min="51" max="52" width="9" style="3" customWidth="1"/>
+    <col min="53" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
@@ -1150,209 +1169,211 @@
         <v>5</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>185</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AQ2" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AU2" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AV2" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW2" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX2" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:50" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA3" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="AB3" s="6" t="s">
-        <v>56</v>
+        <v>192</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AD3" s="6"/>
       <c r="AE3" s="6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AF3" s="6"/>
       <c r="AG3" s="6"/>
@@ -1367,326 +1388,326 @@
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
       <c r="AR3" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AS3" s="6"/>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AW3" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AX3" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AK4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AL4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AM4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AN4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AO4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AP4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AQ4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AR4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AS4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AT4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AU4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AW4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AX4" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="X5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="Y5" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="Z5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AA5" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="AB5" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AJ5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AK5" s="8" t="s">
+      <c r="AP5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AQ5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AL5" s="8" t="s">
+      <c r="AR5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AM5" s="8" t="s">
+      <c r="AS5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AN5" s="8" t="s">
+      <c r="AT5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AO5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AP5" s="8" t="s">
+      <c r="AV5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AQ5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AS5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AT5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AV5" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="AW5" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AX5" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1703,20 +1724,20 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -1725,19 +1746,19 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
@@ -1758,7 +1779,7 @@
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1866,186 +1887,186 @@
     </row>
     <row r="8" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="T8" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="X8" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH8" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN8" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR8" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="U8" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="V8" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="W8" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z8" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB8" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC8" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE8" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF8" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG8" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH8" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="AN8" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="AO8" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP8" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR8" s="10" t="s">
-        <v>124</v>
-      </c>
       <c r="AS8" s="10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="AT8" s="10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="AU8" s="10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AV8" s="10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="AW8" s="10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3">
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q9" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R9" s="3" t="b">
         <v>1</v>
@@ -2069,16 +2090,16 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AE9" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="AF9" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AG9" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AI9" s="3">
         <v>50</v>
@@ -2098,22 +2119,22 @@
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q10" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R10" s="3" t="b">
         <v>0</v>
@@ -2122,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH10" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AI10" s="3">
         <v>30</v>
@@ -2142,31 +2163,31 @@
         <v>1001</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q11" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R11" s="3" t="b">
         <v>1</v>
@@ -2190,16 +2211,16 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AE11" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="AF11" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AI11" s="3">
         <v>50</v>
@@ -2222,16 +2243,16 @@
         <v>1002</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R12" s="3" t="b">
         <v>0</v>
@@ -2240,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH12" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AI12" s="3">
         <v>30</v>
@@ -2260,76 +2281,76 @@
         <v>1003</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="O13" s="3">
         <v>300</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q13" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R13" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Y13" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="Z13" s="3">
         <v>30</v>
       </c>
       <c r="AA13" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB13" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>300</v>
       </c>
       <c r="AC13" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AF13" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH13" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AI13" s="3">
         <v>15</v>
       </c>
       <c r="AK13" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AL13" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AQ13" s="3">
         <v>0</v>
@@ -2343,217 +2364,250 @@
     </row>
     <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>157</v>
+        <v>193</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>186</v>
+      <c r="M14" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q14" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="R14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <v>1005</v>
-      </c>
-      <c r="U14" t="s">
-        <v>159</v>
-      </c>
-      <c r="W14" t="s">
-        <v>160</v>
-      </c>
       <c r="Y14" s="3">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="Z14" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="AC14" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="AD14" t="s">
+        <v>147</v>
+      </c>
       <c r="AE14" s="3" t="s">
-        <v>140</v>
+        <v>67</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>164</v>
       </c>
       <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="3">
-        <v>10</v>
-      </c>
-      <c r="AU14" s="3">
+        <v>40</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>20</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>20</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="3">
         <v>1000</v>
+      </c>
+      <c r="AS14" s="3">
+        <v>5000</v>
       </c>
     </row>
     <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
+        <v>1004</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>167</v>
+      </c>
+      <c r="R15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>1005</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>138</v>
-      </c>
-      <c r="R15" s="3" t="b">
-        <v>0</v>
+      <c r="U15" t="s">
+        <v>168</v>
+      </c>
+      <c r="W15" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>15</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>800</v>
       </c>
       <c r="AC15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>147</v>
+        <v>1</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="AI15" s="3">
-        <v>20</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AT15" s="3">
+        <v>10</v>
+      </c>
+      <c r="AU15" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="T16" s="3">
-        <v>1007</v>
-      </c>
-      <c r="U16" t="s">
-        <v>159</v>
-      </c>
-      <c r="W16" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>80</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>2000</v>
-      </c>
       <c r="AC16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG16" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH16" t="s">
         <v>155</v>
       </c>
       <c r="AI16" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AJ16" s="3">
-        <v>5</v>
-      </c>
-      <c r="AK16" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL16" s="3">
-        <v>50</v>
-      </c>
-      <c r="AQ16" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="3">
-        <v>300</v>
-      </c>
-      <c r="AS16" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
+        <v>1006</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>1007</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>138</v>
-      </c>
-      <c r="R17" s="3" t="b">
-        <v>0</v>
+      <c r="U17" t="s">
+        <v>168</v>
+      </c>
+      <c r="W17" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>2000</v>
       </c>
       <c r="AC17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>174</v>
       </c>
       <c r="AF17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG17" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH17" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AI17" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AJ17" s="3">
         <v>5</v>
@@ -2565,363 +2619,413 @@
         <v>50</v>
       </c>
       <c r="AQ17" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AR17" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AS17" s="3">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q18" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="Y18" s="3">
-        <v>10000</v>
-      </c>
       <c r="AC18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="AF18" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH18" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AI18" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AJ18" s="3">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>50</v>
       </c>
       <c r="AQ18" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AR18" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="AS18" s="3">
+        <v>5000</v>
       </c>
     </row>
     <row r="19" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q19" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="R19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Y19" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AC19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>30</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AQ19" s="3">
         <v>300</v>
       </c>
-      <c r="Z19" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT19" s="3">
-        <v>5</v>
+      <c r="AR19" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q20" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="3">
-        <v>1011</v>
-      </c>
-      <c r="U20" t="s">
-        <v>159</v>
-      </c>
-      <c r="W20" t="s">
-        <v>164</v>
-      </c>
       <c r="Y20" s="3">
-        <v>20000</v>
+        <v>300</v>
       </c>
       <c r="Z20" s="3">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AC20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AD20" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>147</v>
+      <c r="AE20" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="AI20" s="3">
-        <v>50</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>10</v>
-      </c>
-      <c r="AQ20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AR20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AT20" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
+        <v>1010</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>146</v>
+      </c>
+      <c r="R21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>1011</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>138</v>
-      </c>
-      <c r="R21" s="3" t="b">
-        <v>0</v>
+      <c r="U21" t="s">
+        <v>168</v>
+      </c>
+      <c r="W21" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>1000</v>
       </c>
       <c r="AC21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>185</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>67</v>
       </c>
       <c r="AF21" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AH21" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AI21" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AJ21" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AQ21" s="3">
         <v>1000</v>
       </c>
       <c r="AR21" s="3">
         <v>0</v>
-      </c>
-      <c r="AV21" s="3">
-        <v>10</v>
-      </c>
-      <c r="AW21" s="3">
-        <v>10</v>
-      </c>
-      <c r="AX21" s="3">
-        <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
-        <v>9001</v>
+        <v>1011</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>138</v>
+        <v>186</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>146</v>
       </c>
       <c r="R22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="Y22" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>350</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>250</v>
-      </c>
       <c r="AC22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH22" t="s">
         <v>155</v>
       </c>
       <c r="AI22" s="3">
-        <v>5</v>
-      </c>
-      <c r="AK22" s="3">
+        <v>20</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>2</v>
       </c>
-      <c r="AL22" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>2</v>
+      <c r="AQ22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AR22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AW22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AX22" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:50" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="R23" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="AA23" s="3">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="AB23" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AC23" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD23" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AE23" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="AG23" s="3" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="AH23" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="AN23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:50" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>9002</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI24" s="3">
         <v>8</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AJ24" s="3">
         <v>1.5</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AM24" s="3">
         <v>12</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AN24" s="3">
         <v>12</v>
       </c>
     </row>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F944D01-EB7C-4BD1-8DE9-15EC0497DDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E196750-CB9B-4824-9CB2-81B9DAF5B6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skill!$B$8:$AX$9</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="220">
   <si>
     <t>데이터이름</t>
   </si>
@@ -160,6 +157,9 @@
     <t>흩뿌리기 링 영역</t>
   </si>
   <si>
+    <t>효과 중심 전방 오프셋</t>
+  </si>
+  <si>
     <t>컬럼설명세부</t>
   </si>
   <si>
@@ -202,7 +202,7 @@
     <t>다음페이즈 스킬 없으면 0</t>
   </si>
   <si>
-    <t xml:space="preserve">NextTrigger가 AfterDelay일 때만 사용. NextTriggerDelayMs 만큼 지난다음 발동된다. </t>
+    <t>NextTrigger가 AfterDelay일 때만 사용. NextTriggerDelayMs 만큼 지난다음 발동된다.</t>
   </si>
   <si>
     <t>NextOrigin 이 CasterFront일 때만 사용. 앞쪽 거리</t>
@@ -211,6 +211,12 @@
     <t>트리거로 발동되는 스킬에게는 의미없음</t>
   </si>
   <si>
+    <t>스킬 시전 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
+  </si>
+  <si>
+    <t>이 페이즈 동안 캐스터 이동 불가 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
+  </si>
+  <si>
     <t>스킬 시전했을 때 타겟 방향으로 캐릭터가 회전할지 여부</t>
   </si>
   <si>
@@ -439,6 +445,9 @@
     <t>ScatterOuterRadius</t>
   </si>
   <si>
+    <t>EffectCenterForwardOffset</t>
+  </si>
+  <si>
     <t>//</t>
   </si>
   <si>
@@ -469,72 +478,93 @@
     <t>Nearest</t>
   </si>
   <si>
+    <t>SkillCastOrigin</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>ContactHit</t>
+  </si>
+  <si>
+    <t>Fireball_Explosion</t>
+  </si>
+  <si>
+    <t>Claude/VFX/Sorcerer/Fireball/VS_Sorc_Fireball_Impact</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_034</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fireball_Bullet</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fire_CircleShock_modified</t>
+  </si>
+  <si>
+    <t>IceField</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_025</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Ice Skill/Prefabs/FX_Ice_Crack</t>
+  </si>
+  <si>
+    <t>Fire_Magic_2</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Shoot 5 modified</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Cast 5 modified</t>
+  </si>
+  <si>
+    <t>Obb</t>
+  </si>
+  <si>
+    <t>FirePillar</t>
+  </si>
+  <si>
+    <t>불기둥</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_140</t>
+  </si>
+  <si>
+    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_0104</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
+  </si>
+  <si>
+    <t>Glide</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_051</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>AfterEnd</t>
+  </si>
+  <si>
+    <t>PrevEnd</t>
+  </si>
+  <si>
     <t>Caster</t>
   </si>
   <si>
-    <t>Linear</t>
-  </si>
-  <si>
-    <t>ContactHit</t>
-  </si>
-  <si>
-    <t>Fireball_Explosion</t>
-  </si>
-  <si>
-    <t>Claude/VFX/Sorcerer/Fireball/VS_Sorc_Fireball_Impact</t>
-  </si>
-  <si>
-    <t>Static</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_034</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fireball_Bullet</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fire_CircleShock_modified</t>
-  </si>
-  <si>
-    <t>IceField</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Ice Skill/Prefabs/FX_Ice_Crack</t>
-  </si>
-  <si>
-    <t>Fire_Magic_2</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Shoot 5 modified</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Cast 5 modified</t>
-  </si>
-  <si>
-    <t>Obb</t>
-  </si>
-  <si>
-    <t>Glide</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_051</t>
-  </si>
-  <si>
-    <t>Mobility</t>
-  </si>
-  <si>
-    <t>AfterEnd</t>
-  </si>
-  <si>
-    <t>PrevEnd</t>
-  </si>
-  <si>
     <t>Glide_Shockwave</t>
   </si>
   <si>
@@ -547,9 +577,6 @@
     <t>PrevCenter</t>
   </si>
   <si>
-    <t>Forward</t>
-  </si>
-  <si>
     <t>Blaze_FireField</t>
   </si>
   <si>
@@ -577,6 +604,9 @@
     <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Meteor_modified</t>
   </si>
   <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Pure Flames</t>
+  </si>
+  <si>
     <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Hit 3</t>
   </si>
   <si>
@@ -598,44 +628,59 @@
     <t>몬스터 원거리공격</t>
   </si>
   <si>
-    <t>스킬 시전 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 페이즈 동안 캐스터 이동 불가 시간. 주의: CastDelayMs 값은 ActionLockMs 보다 작거나 같아야 함.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FirePillar</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>불기둥</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_025</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_140</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_0104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Pure Flames</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Art/GabrielAguiarProductions_Projectile/UniqueProjectilesVol_4/Prefabs/Projectiles/vfx_Projectile_Arrow06</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dragon_Bite</t>
+  </si>
+  <si>
+    <t>드래곤 물기(잔기술). 짧은 윈드업, 짧은 쿨</t>
+  </si>
+  <si>
+    <t>Art/DragonVFX/FX_FireHit_02</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Dragon_ClawSweep</t>
+  </si>
+  <si>
+    <t>드래곤 할퀴기(전방 광역). 긴 윈드업 = 회피 가능</t>
+  </si>
+  <si>
+    <t>Art/DragonVFX/DragonClawSlash</t>
+  </si>
+  <si>
+    <t>ClawSweep</t>
+  </si>
+  <si>
+    <t>Dragon_FlameBreath</t>
+  </si>
+  <si>
+    <t>드래곤 화염브레스. SkillCastOrigin에서 시작하는 긴 장판(0~24m) + 지속 틱</t>
+  </si>
+  <si>
+    <t>Art/DragonVFX/FX_Dragonfire</t>
+  </si>
+  <si>
+    <t>FlameBreath</t>
+  </si>
+  <si>
+    <t>Dragon_Roar</t>
+  </si>
+  <si>
+    <t>드래곤 포효. 자기중심 광역. 최우선(쿨 길어 가끔)</t>
+  </si>
+  <si>
+    <t>Art/DragonVFX/FX_Fire_CircleShock</t>
+  </si>
+  <si>
+    <t>Roar</t>
+  </si>
+  <si>
+    <t>Placement 기준점에서 효과 중심까지의 전방 거리. 예를들면 빔의 시작점을 SkillCastOrigin에 맞추려면 ObbLength의 절반을 입력한다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -647,30 +692,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -679,7 +714,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -688,13 +722,17 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0A0A0A"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="5">
@@ -718,7 +756,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -784,21 +822,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
@@ -810,23 +848,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="60% - 강조색1" xfId="2" builtinId="32"/>
-    <cellStyle name="메모" xfId="1" builtinId="10"/>
+    <cellStyle name="60% - 강조색1" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="메모" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -840,6 +897,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -885,74 +959,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -964,23 +978,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -990,23 +1004,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1014,26 +1028,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1068,17 +1079,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1095,17 +1106,12 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1122,18 +1128,20 @@
     <col min="17" max="17" width="17.5" style="3" customWidth="1"/>
     <col min="18" max="19" width="19.125" style="3" customWidth="1"/>
     <col min="20" max="20" width="18.25" style="3" customWidth="1"/>
-    <col min="21" max="21" width="23" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" style="3" customWidth="1"/>
     <col min="22" max="22" width="23.125" style="3" customWidth="1"/>
     <col min="23" max="24" width="18.25" style="3" customWidth="1"/>
     <col min="25" max="25" width="20.875" style="3" customWidth="1"/>
-    <col min="26" max="37" width="18.25" style="3" customWidth="1"/>
-    <col min="38" max="38" width="20.75" style="3" customWidth="1"/>
-    <col min="39" max="50" width="18.25" style="3" customWidth="1"/>
-    <col min="51" max="52" width="9" style="3" customWidth="1"/>
-    <col min="53" max="16384" width="9" style="3"/>
+    <col min="26" max="31" width="18.25" style="3" customWidth="1"/>
+    <col min="32" max="32" width="24" style="3" customWidth="1"/>
+    <col min="33" max="38" width="18.25" style="3" customWidth="1"/>
+    <col min="39" max="39" width="20.75" style="3" customWidth="1"/>
+    <col min="40" max="51" width="18.25" style="3" customWidth="1"/>
+    <col min="52" max="53" width="9" style="3" customWidth="1"/>
+    <col min="54" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,8 +1162,43 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
+      <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
+      <c r="AI1"/>
+      <c r="AJ1"/>
+      <c r="AK1"/>
+      <c r="AL1"/>
+      <c r="AM1"/>
+      <c r="AN1"/>
+      <c r="AO1"/>
+      <c r="AP1"/>
+      <c r="AQ1"/>
+      <c r="AR1"/>
+      <c r="AS1"/>
+      <c r="AT1"/>
+      <c r="AU1"/>
+      <c r="AV1"/>
+      <c r="AW1"/>
+      <c r="AX1"/>
+      <c r="AY1"/>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1242,140 +1285,145 @@
         <v>26</v>
       </c>
       <c r="AF2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AH2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AH2" s="4" t="s">
+      <c r="AI2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AK2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AL2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AM2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AO2" s="4" t="s">
+      <c r="AP2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AP2" s="4" t="s">
+      <c r="AQ2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AQ2" s="4" t="s">
+      <c r="AR2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AR2" s="4" t="s">
+      <c r="AS2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AS2" s="4" t="s">
+      <c r="AT2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AT2" s="4" t="s">
+      <c r="AU2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AU2" s="4" t="s">
+      <c r="AV2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AV2" s="4" t="s">
+      <c r="AW2" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="AW2" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AX2" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="AY2" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" spans="1:50" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>191</v>
+        <v>63</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AD3" s="6"/>
       <c r="AE3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF3" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>219</v>
+      </c>
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
@@ -1387,327 +1435,334 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
-      <c r="AR3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AS3" s="6"/>
+      <c r="AR3" s="6"/>
+      <c r="AS3" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
-      <c r="AV3" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="AV3" s="6"/>
       <c r="AW3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX3" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="AY3" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AL4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AM4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AN4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AO4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AP4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AQ4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AR4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AS4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AT4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AU4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AW4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AX4" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="AY4" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="S5" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="T5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI5" s="8" t="s">
         <v>77</v>
       </c>
       <c r="AJ5" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AK5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AL5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AM5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AN5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AO5" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AP5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AQ5" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AR5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AS5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AT5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AU5" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AV5" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AW5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AX5" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="AY5" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1724,20 +1779,20 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -1746,21 +1801,21 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF6" s="8" t="s">
-        <v>85</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AF6" s="8"/>
       <c r="AG6" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI6" s="8"/>
+        <v>89</v>
+      </c>
+      <c r="AI6" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
       <c r="AL6" s="8"/>
@@ -1776,10 +1831,11 @@
       <c r="AV6" s="8"/>
       <c r="AW6" s="8"/>
       <c r="AX6" s="8"/>
+      <c r="AY6" s="8"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1799,7 +1855,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="8" t="b">
+      <c r="R7" s="14" t="b">
         <v>0</v>
       </c>
       <c r="S7" s="8">
@@ -1828,17 +1884,17 @@
       <c r="AB7" s="8">
         <v>0</v>
       </c>
-      <c r="AC7" s="8" t="b">
+      <c r="AC7" s="14" t="b">
         <v>1</v>
       </c>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
+      <c r="AF7" s="8">
+        <v>0</v>
+      </c>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
-      <c r="AI7" s="8">
-        <v>0</v>
-      </c>
+      <c r="AI7" s="8"/>
       <c r="AJ7" s="8">
         <v>0</v>
       </c>
@@ -1884,196 +1940,214 @@
       <c r="AX7" s="8">
         <v>0</v>
       </c>
+      <c r="AY7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:51" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AT8" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AU8" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AV8" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AW8" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="AY8" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B9" s="3">
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
       <c r="G9" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="H9"/>
       <c r="I9" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K9"/>
       <c r="L9" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="M9"/>
       <c r="N9" s="3" t="s">
-        <v>144</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O9"/>
       <c r="P9" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q9" t="s">
-        <v>146</v>
-      </c>
-      <c r="R9" s="3" t="b">
+        <v>150</v>
+      </c>
+      <c r="R9" s="15" t="b">
         <v>1</v>
       </c>
       <c r="S9" s="3">
         <v>1002</v>
       </c>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
@@ -2086,115 +2160,182 @@
       <c r="AB9" s="3">
         <v>300</v>
       </c>
-      <c r="AC9" s="3" t="b">
+      <c r="AC9" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE9" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI9" s="3">
+        <v>153</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI9"/>
+      <c r="AJ9" s="3">
         <v>50</v>
       </c>
-      <c r="AM9" s="3">
-        <v>15</v>
-      </c>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
       <c r="AN9" s="3">
         <v>15</v>
       </c>
       <c r="AO9" s="3">
+        <v>15</v>
+      </c>
+      <c r="AP9" s="3">
         <v>5</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>90</v>
       </c>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
       <c r="H10" s="3" t="s">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
       <c r="P10" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q10" t="s">
-        <v>146</v>
-      </c>
-      <c r="R10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="R10" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10">
+        <v>0</v>
       </c>
       <c r="AG10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI10" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>30</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5</v>
       </c>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A11"/>
       <c r="B11" s="3">
         <v>1001</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D11"/>
       <c r="E11" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F11"/>
       <c r="G11" s="3" t="s">
-        <v>157</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="H11"/>
       <c r="I11" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K11"/>
       <c r="L11" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="M11"/>
       <c r="N11" s="3" t="s">
-        <v>144</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O11"/>
       <c r="P11" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="s">
-        <v>146</v>
-      </c>
-      <c r="R11" s="3" t="b">
+        <v>150</v>
+      </c>
+      <c r="R11" s="15" t="b">
         <v>1</v>
       </c>
       <c r="S11" s="3">
         <v>1002</v>
       </c>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
       <c r="Y11" s="3">
         <v>0</v>
       </c>
@@ -2207,112 +2348,180 @@
       <c r="AB11" s="3">
         <v>300</v>
       </c>
-      <c r="AC11" s="3" t="b">
+      <c r="AC11" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE11" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
       </c>
       <c r="AG11" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI11" s="3">
+        <v>153</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI11"/>
+      <c r="AJ11" s="3">
         <v>50</v>
       </c>
-      <c r="AM11" s="3">
-        <v>15</v>
-      </c>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
       <c r="AN11" s="3">
         <v>15</v>
       </c>
       <c r="AO11" s="3">
+        <v>15</v>
+      </c>
+      <c r="AP11" s="3">
         <v>5</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AQ11" s="3">
         <v>90</v>
       </c>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A12"/>
       <c r="B12" s="3">
         <v>1002</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
       <c r="H12" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>150</v>
+      </c>
+      <c r="R12" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH12" t="s">
         <v>158</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>146</v>
-      </c>
-      <c r="R12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI12" s="3">
+      <c r="AI12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>30</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5</v>
       </c>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A13"/>
       <c r="B13" s="3">
         <v>1003</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>159</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="D13"/>
       <c r="E13" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13"/>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="K13"/>
       <c r="L13" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="M13"/>
       <c r="N13" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="O13" s="3">
         <v>300</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q13" t="s">
-        <v>146</v>
-      </c>
-      <c r="R13" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R13" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
       <c r="Y13" s="3">
         <v>5000</v>
       </c>
@@ -2325,77 +2534,103 @@
       <c r="AB13" s="3">
         <v>1000</v>
       </c>
-      <c r="AC13" s="3" t="b">
+      <c r="AC13" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>153</v>
+        <v>70</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
       </c>
       <c r="AG13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH13" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI13" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ13" s="3">
         <v>15</v>
       </c>
-      <c r="AK13" s="3">
-        <v>10</v>
-      </c>
+      <c r="AK13"/>
       <c r="AL13" s="3">
         <v>10</v>
       </c>
-      <c r="AQ13" s="3">
-        <v>0</v>
-      </c>
+      <c r="AM13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
       <c r="AR13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="3">
         <v>1000</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="AT13" s="3">
         <v>2000</v>
       </c>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A14"/>
       <c r="B14" s="3">
         <v>1008</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
       <c r="H14" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14"/>
       <c r="M14" s="3" t="s">
-        <v>199</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14"/>
+      <c r="O14"/>
       <c r="P14" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q14" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R14" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
       <c r="Y14" s="3">
         <v>10000</v>
       </c>
@@ -2408,77 +2643,103 @@
       <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3" t="b">
+      <c r="AC14" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>153</v>
+        <v>70</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI14" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>40</v>
       </c>
-      <c r="AK14" s="3">
-        <v>20</v>
-      </c>
+      <c r="AK14"/>
       <c r="AL14" s="3">
         <v>20</v>
       </c>
-      <c r="AQ14" s="3">
-        <v>0</v>
-      </c>
+      <c r="AM14" s="3">
+        <v>20</v>
+      </c>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
       <c r="AR14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="3">
         <v>1000</v>
       </c>
-      <c r="AS14" s="3">
+      <c r="AT14" s="3">
         <v>5000</v>
       </c>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A15"/>
       <c r="B15" s="3">
         <v>1004</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>165</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D15"/>
       <c r="E15" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
       <c r="I15" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
       <c r="P15" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q15" t="s">
-        <v>167</v>
-      </c>
-      <c r="R15" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="R15" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15"/>
       <c r="T15" s="3">
         <v>1005</v>
       </c>
       <c r="U15" t="s">
-        <v>168</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="V15"/>
       <c r="W15" t="s">
-        <v>169</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="X15"/>
       <c r="Y15" s="3">
         <v>600</v>
       </c>
@@ -2491,91 +2752,166 @@
       <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AC15" s="3" t="b">
+      <c r="AC15" s="15" t="b">
         <v>1</v>
       </c>
+      <c r="AD15"/>
       <c r="AE15" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="3">
+        <v>180</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15"/>
+      <c r="AH15"/>
+      <c r="AI15"/>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15"/>
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
+      <c r="AU15" s="3">
         <v>10</v>
       </c>
-      <c r="AU15" s="3">
+      <c r="AV15" s="3">
         <v>1000</v>
       </c>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A16"/>
       <c r="B16" s="3">
         <v>1005</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>170</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
       <c r="P16" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q16" t="s">
-        <v>146</v>
-      </c>
-      <c r="R16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="R16" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16">
+        <v>0</v>
       </c>
       <c r="AG16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH16" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI16" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ16" s="3">
         <v>20</v>
       </c>
-      <c r="AJ16" s="3">
+      <c r="AK16" s="3">
         <v>3</v>
       </c>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
+      <c r="AS16"/>
+      <c r="AT16"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16"/>
+      <c r="AX16"/>
+      <c r="AY16"/>
     </row>
-    <row r="17" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A17"/>
       <c r="B17" s="3">
         <v>1006</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D17"/>
       <c r="E17" s="3" t="s">
-        <v>172</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
       <c r="I17" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
       <c r="P17" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q17" t="s">
-        <v>146</v>
-      </c>
-      <c r="R17" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R17" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17"/>
       <c r="T17" s="3">
         <v>1007</v>
       </c>
       <c r="U17" t="s">
-        <v>168</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="V17"/>
       <c r="W17" t="s">
-        <v>173</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="X17"/>
       <c r="Y17" s="3">
         <v>20000</v>
       </c>
@@ -2588,177 +2924,277 @@
       <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AC17" s="3" t="b">
+      <c r="AC17" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>153</v>
+        <v>180</v>
+      </c>
+      <c r="AF17">
+        <v>25</v>
       </c>
       <c r="AG17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI17" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>40</v>
-      </c>
-      <c r="AJ17" s="3">
-        <v>5</v>
       </c>
       <c r="AK17" s="3">
         <v>5</v>
       </c>
       <c r="AL17" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
         <v>50</v>
       </c>
-      <c r="AQ17" s="3">
-        <v>0</v>
-      </c>
+      <c r="AN17"/>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
       <c r="AR17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="3">
         <v>300</v>
       </c>
-      <c r="AS17" s="3">
+      <c r="AT17" s="3">
         <v>3000</v>
       </c>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17"/>
+      <c r="AX17"/>
+      <c r="AY17"/>
     </row>
-    <row r="18" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A18"/>
       <c r="B18" s="3">
         <v>1007</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
       <c r="P18" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q18" t="s">
-        <v>146</v>
-      </c>
-      <c r="R18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="R18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18">
+        <v>0</v>
       </c>
       <c r="AG18" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH18" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI18" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>15</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>5</v>
       </c>
       <c r="AK18" s="3">
         <v>5</v>
       </c>
       <c r="AL18" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3">
         <v>50</v>
       </c>
-      <c r="AQ18" s="3">
-        <v>1000</v>
-      </c>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
       <c r="AR18" s="3">
         <v>1000</v>
       </c>
       <c r="AS18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AT18" s="3">
         <v>5000</v>
       </c>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
     </row>
-    <row r="19" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A19"/>
       <c r="B19" s="3">
         <v>1012</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>176</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D19"/>
       <c r="E19" s="3" t="s">
-        <v>177</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
       <c r="I19" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
       <c r="P19" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q19" t="s">
-        <v>146</v>
-      </c>
-      <c r="R19" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R19" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
       <c r="Y19" s="3">
         <v>10000</v>
       </c>
-      <c r="AC19" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19"/>
       <c r="AE19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>153</v>
+        <v>180</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH19" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI19" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ19" s="3">
         <v>30</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AK19" s="3">
         <v>10</v>
       </c>
-      <c r="AQ19" s="3">
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19" s="3">
         <v>300</v>
       </c>
-      <c r="AR19" s="3">
-        <v>0</v>
-      </c>
+      <c r="AS19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT19"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
     </row>
-    <row r="20" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A20"/>
       <c r="B20" s="3">
         <v>1009</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D20"/>
       <c r="E20" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
       <c r="P20" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q20" t="s">
-        <v>167</v>
-      </c>
-      <c r="R20" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="R20" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
       <c r="Y20" s="3">
         <v>300</v>
       </c>
@@ -2771,65 +3207,95 @@
       <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3" t="b">
+      <c r="AC20" s="15" t="b">
         <v>1</v>
       </c>
+      <c r="AD20"/>
       <c r="AE20" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="3">
+        <v>180</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20"/>
+      <c r="AH20"/>
+      <c r="AI20"/>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20"/>
+      <c r="AL20"/>
+      <c r="AM20"/>
+      <c r="AN20"/>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20"/>
+      <c r="AS20"/>
+      <c r="AT20"/>
+      <c r="AU20" s="3">
         <v>5</v>
       </c>
+      <c r="AV20"/>
+      <c r="AW20"/>
+      <c r="AX20"/>
+      <c r="AY20"/>
     </row>
-    <row r="21" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A21"/>
       <c r="B21" s="3">
         <v>1010</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D21"/>
       <c r="E21" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G21"/>
       <c r="H21" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K21"/>
+      <c r="L21"/>
       <c r="M21" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="O21"/>
       <c r="P21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q21" t="s">
-        <v>146</v>
-      </c>
-      <c r="R21" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R21" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21"/>
       <c r="T21" s="3">
         <v>1011</v>
       </c>
       <c r="U21" t="s">
-        <v>168</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="V21"/>
       <c r="W21" t="s">
-        <v>173</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="X21"/>
       <c r="Y21" s="3">
         <v>20000</v>
       </c>
@@ -2842,197 +3308,693 @@
       <c r="AB21" s="3">
         <v>1000</v>
       </c>
-      <c r="AC21" s="3" t="b">
+      <c r="AC21" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="AE21" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>153</v>
+        <v>70</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
       </c>
       <c r="AG21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI21" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>50</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AL21"/>
+      <c r="AM21"/>
+      <c r="AN21"/>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21" s="3">
         <v>1000</v>
       </c>
-      <c r="AR21" s="3">
-        <v>0</v>
-      </c>
+      <c r="AS21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT21"/>
+      <c r="AU21"/>
+      <c r="AV21"/>
+      <c r="AW21"/>
+      <c r="AX21"/>
+      <c r="AY21"/>
     </row>
-    <row r="22" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A22"/>
       <c r="B22" s="3">
         <v>1011</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>186</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
       <c r="P22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q22" t="s">
-        <v>146</v>
-      </c>
-      <c r="R22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="R22" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22">
+        <v>0</v>
       </c>
       <c r="AG22" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH22" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI22" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>20</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2</v>
       </c>
-      <c r="AQ22" s="3">
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22" s="3">
         <v>1000</v>
       </c>
-      <c r="AR22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV22" s="3">
-        <v>10</v>
-      </c>
+      <c r="AS22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
       <c r="AW22" s="3">
         <v>10</v>
       </c>
       <c r="AX22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AY22" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A23"/>
       <c r="B23" s="3">
         <v>9001</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>188</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
       <c r="Q23" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="R23" s="3" t="b">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R23" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
       <c r="Y23" s="3">
         <v>1500</v>
       </c>
+      <c r="Z23"/>
       <c r="AA23" s="3">
         <v>350</v>
       </c>
       <c r="AB23" s="3">
         <v>250</v>
       </c>
-      <c r="AC23" s="3" t="b">
+      <c r="AC23" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG23" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="AG23"/>
       <c r="AH23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI23" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>5</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AK23"/>
+      <c r="AL23" s="3">
         <v>2</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2.5</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AN23"/>
+      <c r="AO23" s="3">
         <v>2</v>
       </c>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
     </row>
-    <row r="24" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A24"/>
       <c r="B24" s="3">
         <v>9002</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="E24"/>
+      <c r="F24"/>
       <c r="G24" s="3" t="s">
-        <v>200</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
       <c r="Q24" s="3" t="s">
-        <v>146</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
       <c r="Y24" s="3">
         <v>4000</v>
       </c>
+      <c r="Z24"/>
       <c r="AA24" s="3">
         <v>600</v>
       </c>
       <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3" t="b">
+      <c r="AC24" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD24" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24"/>
       <c r="AH24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI24" s="3">
+        <v>154</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>8</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1.5</v>
       </c>
-      <c r="AM24" s="3">
-        <v>12</v>
-      </c>
+      <c r="AL24"/>
+      <c r="AM24"/>
       <c r="AN24" s="3">
         <v>12</v>
       </c>
+      <c r="AO24" s="3">
+        <v>12</v>
+      </c>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24"/>
+      <c r="AS24"/>
+      <c r="AT24"/>
+      <c r="AU24"/>
+      <c r="AV24"/>
+      <c r="AW24"/>
+      <c r="AX24"/>
+      <c r="AY24"/>
+    </row>
+    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A25"/>
+      <c r="B25" s="3">
+        <v>9101</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25" t="s">
+        <v>205</v>
+      </c>
+      <c r="I25" t="s">
+        <v>206</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Z25"/>
+      <c r="AA25" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>350</v>
+      </c>
+      <c r="AC25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>4</v>
+      </c>
+      <c r="AG25"/>
+      <c r="AH25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI25" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>12</v>
+      </c>
+      <c r="AK25"/>
+      <c r="AL25" s="3">
+        <v>4</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>8</v>
+      </c>
+      <c r="AN25"/>
+      <c r="AO25" s="3">
+        <v>8</v>
+      </c>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25"/>
+      <c r="AS25"/>
+      <c r="AT25"/>
+      <c r="AU25"/>
+      <c r="AV25"/>
+      <c r="AW25"/>
+      <c r="AX25"/>
+      <c r="AY25"/>
+    </row>
+    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A26"/>
+      <c r="B26" s="3">
+        <v>9102</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26" t="s">
+        <v>209</v>
+      </c>
+      <c r="I26" t="s">
+        <v>210</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Z26"/>
+      <c r="AA26" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="AG26"/>
+      <c r="AH26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>22</v>
+      </c>
+      <c r="AK26"/>
+      <c r="AL26" s="3">
+        <v>12</v>
+      </c>
+      <c r="AM26" s="3">
+        <v>9</v>
+      </c>
+      <c r="AN26"/>
+      <c r="AO26" s="3">
+        <v>9</v>
+      </c>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26"/>
+      <c r="AS26"/>
+      <c r="AT26"/>
+      <c r="AU26"/>
+      <c r="AV26"/>
+      <c r="AW26"/>
+      <c r="AX26"/>
+      <c r="AY26"/>
+    </row>
+    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A27"/>
+      <c r="B27" s="3">
+        <v>9103</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27" t="s">
+        <v>213</v>
+      </c>
+      <c r="I27" t="s">
+        <v>214</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27">
+        <v>14</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Z27"/>
+      <c r="AA27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC27" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>8</v>
+      </c>
+      <c r="AK27"/>
+      <c r="AL27" s="3">
+        <v>8</v>
+      </c>
+      <c r="AM27" s="3">
+        <v>24</v>
+      </c>
+      <c r="AN27"/>
+      <c r="AO27" s="3">
+        <v>24</v>
+      </c>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>400</v>
+      </c>
+      <c r="AT27">
+        <v>2000</v>
+      </c>
+      <c r="AU27"/>
+      <c r="AV27"/>
+      <c r="AW27"/>
+      <c r="AX27"/>
+      <c r="AY27"/>
+    </row>
+    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A28"/>
+      <c r="B28" s="3">
+        <v>9104</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" t="s">
+        <v>218</v>
+      </c>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z28"/>
+      <c r="AA28" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC28" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH28" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>15</v>
+      </c>
+      <c r="AK28">
+        <v>14</v>
+      </c>
+      <c r="AL28"/>
+      <c r="AM28"/>
+      <c r="AN28"/>
+      <c r="AO28" s="3">
+        <v>14</v>
+      </c>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28"/>
+      <c r="AS28"/>
+      <c r="AT28"/>
+      <c r="AU28"/>
+      <c r="AV28"/>
+      <c r="AW28"/>
+      <c r="AX28"/>
+      <c r="AY28"/>
     </row>
   </sheetData>
-  <autoFilter ref="B8:AX9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E196750-CB9B-4824-9CB2-81B9DAF5B6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F07CAE3-2963-4035-A248-4D60436322DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="230">
   <si>
     <t>데이터이름</t>
   </si>
@@ -103,6 +103,9 @@
     <t>스킬 효과의 위치</t>
   </si>
   <si>
+    <t>효과 중심 전방 오프셋</t>
+  </si>
+  <si>
     <t>스킬 효과의 이동타입</t>
   </si>
   <si>
@@ -157,9 +160,6 @@
     <t>흩뿌리기 링 영역</t>
   </si>
   <si>
-    <t>효과 중심 전방 오프셋</t>
-  </si>
-  <si>
     <t>컬럼설명세부</t>
   </si>
   <si>
@@ -223,6 +223,9 @@
     <t>참고: 다음페이즈 스킬의 경우에는 위치를 NextOrigin이 결정하기 때문에 이 필드를 쓰지않는다.</t>
   </si>
   <si>
+    <t>Placement 기준점에서 효과 중심까지의 전방 거리. 예를들면 빔의 시작점을 SkillCastOrigin에 맞추려면 ObbLength의 절반을 입력한다.</t>
+  </si>
+  <si>
     <t>0이면 단일 틱=instant</t>
   </si>
   <si>
@@ -388,6 +391,9 @@
     <t>Placement</t>
   </si>
   <si>
+    <t>EffectCenterForwardOffset</t>
+  </si>
+  <si>
     <t>EffectMotion</t>
   </si>
   <si>
@@ -445,108 +451,99 @@
     <t>ScatterOuterRadius</t>
   </si>
   <si>
-    <t>EffectCenterForwardOffset</t>
+    <t>Fireball</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_034</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fireball_Bullet</t>
+  </si>
+  <si>
+    <t>Cast_Magic</t>
+  </si>
+  <si>
+    <t>Fire_Magic_1</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Cast 4 modified</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Hit 1 modified</t>
+  </si>
+  <si>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Stationary</t>
+  </si>
+  <si>
+    <t>Nearest</t>
+  </si>
+  <si>
+    <t>SkillCastOrigin</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>ContactHit</t>
+  </si>
+  <si>
+    <t>Fireball_Explosion</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fire_CircleShock_modified</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>IceField</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_025</t>
+  </si>
+  <si>
+    <t>Art/Six Elements VFX Mega Pack/FX_Ice Skill/Prefabs/FX_Ice_Crack</t>
+  </si>
+  <si>
+    <t>Fire_Magic_2</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Shoot 5 modified</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Cast 5 modified</t>
+  </si>
+  <si>
+    <t>Obb</t>
+  </si>
+  <si>
+    <t>FirePillar</t>
+  </si>
+  <si>
+    <t>불기둥</t>
+  </si>
+  <si>
+    <t>Art/SkillIcons/skill_140</t>
+  </si>
+  <si>
+    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_0104</t>
+  </si>
+  <si>
+    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
   </si>
   <si>
     <t>//</t>
   </si>
   <si>
-    <t>Fireball</t>
-  </si>
-  <si>
-    <t>Claude/VFX/Sorcerer/Fireball/VS_Sorc_Fireball</t>
-  </si>
-  <si>
-    <t>Cast_Magic</t>
-  </si>
-  <si>
-    <t>Fire_Magic_1</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Cast 4 modified</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Fire Spell - Hit 1 modified</t>
-  </si>
-  <si>
-    <t>Mage</t>
-  </si>
-  <si>
-    <t>Stationary</t>
-  </si>
-  <si>
-    <t>Nearest</t>
-  </si>
-  <si>
-    <t>SkillCastOrigin</t>
-  </si>
-  <si>
-    <t>Linear</t>
-  </si>
-  <si>
-    <t>ContactHit</t>
-  </si>
-  <si>
-    <t>Fireball_Explosion</t>
-  </si>
-  <si>
-    <t>Claude/VFX/Sorcerer/Fireball/VS_Sorc_Fireball_Impact</t>
-  </si>
-  <si>
-    <t>Static</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_034</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fireball_Bullet</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Fire Skill/Prefabs/FX_Fire_CircleShock_modified</t>
-  </si>
-  <si>
-    <t>IceField</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_025</t>
-  </si>
-  <si>
-    <t>Art/Six Elements VFX Mega Pack/FX_Ice Skill/Prefabs/FX_Ice_Crack</t>
-  </si>
-  <si>
-    <t>Fire_Magic_2</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Shoot 5 modified</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Ice Spell - Cast 5 modified</t>
-  </si>
-  <si>
-    <t>Obb</t>
-  </si>
-  <si>
-    <t>FirePillar</t>
-  </si>
-  <si>
-    <t>불기둥</t>
-  </si>
-  <si>
-    <t>Art/SkillIcons/skill_140</t>
-  </si>
-  <si>
-    <t>Art/Hun0FX/FX/FireFX_vol1/Prefabs/FX_Fire_0104</t>
-  </si>
-  <si>
-    <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
-  </si>
-  <si>
     <t>Glide</t>
   </si>
   <si>
@@ -679,8 +676,40 @@
     <t>Roar</t>
   </si>
   <si>
-    <t>Placement 기준점에서 효과 중심까지의 전방 거리. 예를들면 빔의 시작점을 SkillCastOrigin에 맞추려면 ObbLength의 절반을 입력한다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>Warrior_NarrowSlash</t>
+  </si>
+  <si>
+    <t>전사 전방 좁은 범위 1회 즉발 공격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/NarrowSlash</t>
+  </si>
+  <si>
+    <t>Melee_1</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Warrior_WideSlash</t>
+  </si>
+  <si>
+    <t>전사 전방 넓은 범위 1회 즉발 공격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/WideSlash</t>
+  </si>
+  <si>
+    <t>Melee_2</t>
+  </si>
+  <si>
+    <t>Warrior_MultiSlash</t>
+  </si>
+  <si>
+    <t>전사 캐릭터 주변 좁은 범위 빠른 5회 타격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/MultiSlash</t>
   </si>
 </sst>
 </file>
@@ -822,7 +851,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -879,6 +908,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1111,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1285,64 +1322,64 @@
         <v>26</v>
       </c>
       <c r="AF2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AG2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AS2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AT2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AU2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AV2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AW2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AX2" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="AY2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:51" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
@@ -1422,7 +1459,7 @@
         <v>66</v>
       </c>
       <c r="AF3" s="16" t="s">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
@@ -1437,332 +1474,332 @@
       <c r="AQ3" s="6"/>
       <c r="AR3" s="6"/>
       <c r="AS3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
       <c r="AW3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AX3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AY3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="Q4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AL4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AM4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AN4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AO4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AP4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AQ4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AR4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AS4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AT4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AU4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AW4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AX4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AY4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="P5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="U5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="W5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="AQ5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="AS5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ5" s="8" t="s">
+      <c r="AT5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AU5" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="AV5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AW5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX5" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY5" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1779,20 +1816,20 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -1801,20 +1838,20 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AF6" s="8"/>
       <c r="AG6" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
@@ -1835,7 +1872,7 @@
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1946,163 +1983,161 @@
     </row>
     <row r="8" spans="1:51" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AF8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN8" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS8" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AU8" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AV8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="AX8" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="AG8" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH8" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL8" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="AN8" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="AO8" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP8" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR8" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="AS8" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AT8" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="AU8" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="AV8" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="AW8" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="AX8" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="AY8" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>142</v>
-      </c>
+      <c r="A9"/>
       <c r="B9" s="3">
         <v>1001</v>
       </c>
@@ -2110,32 +2145,34 @@
         <v>143</v>
       </c>
       <c r="D9"/>
-      <c r="E9"/>
+      <c r="E9" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="F9"/>
       <c r="G9" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H9"/>
       <c r="I9" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K9"/>
       <c r="L9" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M9"/>
       <c r="N9" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O9"/>
       <c r="P9" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R9" s="15" t="b">
         <v>1</v>
@@ -2164,19 +2201,19 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AF9">
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AH9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AI9"/>
       <c r="AJ9" s="3">
@@ -2207,21 +2244,19 @@
       <c r="AY9"/>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>142</v>
-      </c>
+      <c r="A10"/>
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -2231,10 +2266,10 @@
       <c r="N10"/>
       <c r="O10"/>
       <c r="P10" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R10" s="15" t="b">
         <v>0</v>
@@ -2258,13 +2293,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AJ10" s="3">
         <v>30</v>
@@ -2290,104 +2325,108 @@
     <row r="11" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A11"/>
       <c r="B11" s="3">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D11"/>
       <c r="E11" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F11"/>
-      <c r="G11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H11"/>
+      <c r="G11"/>
+      <c r="H11" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="I11" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="K11"/>
       <c r="L11" s="3" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="M11"/>
       <c r="N11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="O11"/>
+        <v>166</v>
+      </c>
+      <c r="O11" s="3">
+        <v>300</v>
+      </c>
       <c r="P11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S11" s="3">
-        <v>1002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11"/>
       <c r="T11"/>
       <c r="U11"/>
       <c r="V11"/>
       <c r="W11"/>
       <c r="X11"/>
       <c r="Y11" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Z11" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AA11" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AB11" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AC11" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE11" t="s">
         <v>152</v>
       </c>
-      <c r="AF11">
+      <c r="AE11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF11" s="3">
         <v>0</v>
       </c>
       <c r="AG11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AH11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AI11"/>
+        <v>159</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>167</v>
+      </c>
       <c r="AJ11" s="3">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AK11"/>
-      <c r="AL11"/>
-      <c r="AM11"/>
-      <c r="AN11" s="3">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="3">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ11" s="3">
-        <v>90</v>
-      </c>
-      <c r="AR11"/>
-      <c r="AS11"/>
-      <c r="AT11"/>
+      <c r="AL11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AT11" s="3">
+        <v>2000</v>
+      </c>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -2397,30 +2436,40 @@
     <row r="12" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A12"/>
       <c r="B12" s="3">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12"/>
-      <c r="E12"/>
+        <v>168</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I12"/>
-      <c r="J12"/>
+        <v>171</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="K12"/>
       <c r="L12"/>
-      <c r="M12"/>
+      <c r="M12" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R12" s="15" t="b">
         <v>0</v>
@@ -2431,42 +2480,62 @@
       <c r="V12"/>
       <c r="W12"/>
       <c r="X12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12"/>
-      <c r="AB12"/>
+      <c r="Y12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>30</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>500</v>
+      </c>
       <c r="AC12" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD12"/>
-      <c r="AE12"/>
-      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF12" s="3">
         <v>0</v>
       </c>
       <c r="AG12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AJ12" s="3">
-        <v>30</v>
-      </c>
-      <c r="AK12" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL12"/>
-      <c r="AM12"/>
+        <v>40</v>
+      </c>
+      <c r="AK12"/>
+      <c r="AL12" s="3">
+        <v>20</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>20</v>
+      </c>
       <c r="AN12"/>
       <c r="AO12"/>
       <c r="AP12"/>
       <c r="AQ12"/>
-      <c r="AR12"/>
-      <c r="AS12"/>
-      <c r="AT12"/>
+      <c r="AR12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AT12" s="3">
+        <v>5000</v>
+      </c>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -2474,153 +2543,129 @@
       <c r="AY12"/>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A13"/>
+      <c r="A13" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B13" s="3">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D13"/>
       <c r="E13" s="3" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="H13"/>
       <c r="I13" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="K13"/>
-      <c r="L13" s="3" t="s">
-        <v>167</v>
-      </c>
+      <c r="L13"/>
       <c r="M13"/>
-      <c r="N13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="O13" s="3">
-        <v>300</v>
-      </c>
+      <c r="N13"/>
+      <c r="O13"/>
       <c r="P13" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q13" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="R13" s="15" t="b">
         <v>0</v>
       </c>
       <c r="S13"/>
-      <c r="T13"/>
-      <c r="U13"/>
+      <c r="T13" s="3">
+        <v>1005</v>
+      </c>
+      <c r="U13" t="s">
+        <v>177</v>
+      </c>
       <c r="V13"/>
-      <c r="W13"/>
+      <c r="W13" t="s">
+        <v>178</v>
+      </c>
       <c r="X13"/>
       <c r="Y13" s="3">
-        <v>5000</v>
+        <v>600</v>
       </c>
       <c r="Z13" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AA13" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AC13" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="AD13" t="s">
-        <v>151</v>
-      </c>
+      <c r="AD13"/>
       <c r="AE13" s="3" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-      <c r="AG13" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>169</v>
-      </c>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
       <c r="AJ13" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK13"/>
-      <c r="AL13" s="3">
-        <v>10</v>
-      </c>
-      <c r="AM13" s="3">
-        <v>10</v>
-      </c>
+      <c r="AL13"/>
+      <c r="AM13"/>
       <c r="AN13"/>
       <c r="AO13"/>
       <c r="AP13"/>
       <c r="AQ13"/>
-      <c r="AR13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="3">
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AV13" s="3">
         <v>1000</v>
       </c>
-      <c r="AT13" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AU13"/>
-      <c r="AV13"/>
       <c r="AW13"/>
       <c r="AX13"/>
       <c r="AY13"/>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A14"/>
+      <c r="A14" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B14" s="3">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>172</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
-      <c r="H14" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
-      <c r="M14" s="3" t="s">
-        <v>174</v>
-      </c>
+      <c r="M14"/>
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R14" s="15" t="b">
         <v>0</v>
@@ -2631,62 +2676,42 @@
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
-      <c r="Y14" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>30</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>500</v>
-      </c>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
       <c r="AC14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14">
         <v>0</v>
       </c>
       <c r="AG14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI14" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AJ14" s="3">
-        <v>40</v>
-      </c>
-      <c r="AK14"/>
-      <c r="AL14" s="3">
         <v>20</v>
       </c>
-      <c r="AM14" s="3">
-        <v>20</v>
-      </c>
+      <c r="AK14" s="3">
+        <v>3</v>
+      </c>
+      <c r="AL14"/>
+      <c r="AM14"/>
       <c r="AN14"/>
       <c r="AO14"/>
       <c r="AP14"/>
       <c r="AQ14"/>
-      <c r="AR14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AT14" s="3">
-        <v>5000</v>
-      </c>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -2694,25 +2719,27 @@
       <c r="AY14"/>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A15"/>
+      <c r="A15" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B15" s="3">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D15"/>
       <c r="E15" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K15"/>
       <c r="L15"/>
@@ -2720,81 +2747,99 @@
       <c r="N15"/>
       <c r="O15"/>
       <c r="P15" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="R15" s="15" t="b">
         <v>0</v>
       </c>
       <c r="S15"/>
       <c r="T15" s="3">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="U15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="X15"/>
       <c r="Y15" s="3">
-        <v>600</v>
+        <v>20000</v>
       </c>
       <c r="Z15" s="3">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="AA15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB15" s="3">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="AC15" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="AD15"/>
-      <c r="AE15" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG15"/>
-      <c r="AH15"/>
-      <c r="AI15"/>
+      <c r="AD15" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF15">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>167</v>
+      </c>
       <c r="AJ15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK15"/>
-      <c r="AL15"/>
-      <c r="AM15"/>
+        <v>40</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>50</v>
+      </c>
       <c r="AN15"/>
       <c r="AO15"/>
       <c r="AP15"/>
       <c r="AQ15"/>
-      <c r="AR15"/>
-      <c r="AS15"/>
-      <c r="AT15"/>
-      <c r="AU15" s="3">
-        <v>10</v>
-      </c>
-      <c r="AV15" s="3">
-        <v>1000</v>
-      </c>
+      <c r="AR15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AT15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AU15"/>
+      <c r="AV15"/>
       <c r="AW15"/>
       <c r="AX15"/>
       <c r="AY15"/>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A16"/>
+      <c r="A16" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B16" s="3">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -2809,10 +2854,10 @@
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R16" s="15" t="b">
         <v>0</v>
@@ -2836,29 +2881,39 @@
         <v>0</v>
       </c>
       <c r="AG16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI16" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AJ16" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AK16" s="3">
-        <v>3</v>
-      </c>
-      <c r="AL16"/>
-      <c r="AM16"/>
+        <v>5</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="3">
+        <v>50</v>
+      </c>
       <c r="AN16"/>
       <c r="AO16"/>
       <c r="AP16"/>
       <c r="AQ16"/>
-      <c r="AR16"/>
-      <c r="AS16"/>
-      <c r="AT16"/>
+      <c r="AR16" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AS16" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AT16" s="3">
+        <v>5000</v>
+      </c>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -2866,25 +2921,27 @@
       <c r="AY16"/>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A17"/>
+      <c r="A17" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B17" s="3">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D17"/>
       <c r="E17" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
@@ -2892,84 +2949,64 @@
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R17" s="15" t="b">
         <v>0</v>
       </c>
       <c r="S17"/>
-      <c r="T17" s="3">
-        <v>1007</v>
-      </c>
-      <c r="U17" t="s">
-        <v>178</v>
-      </c>
+      <c r="T17"/>
+      <c r="U17"/>
       <c r="V17"/>
-      <c r="W17" t="s">
-        <v>184</v>
-      </c>
+      <c r="W17"/>
       <c r="X17"/>
       <c r="Y17" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>80</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>2000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
       <c r="AC17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF17">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="AD17"/>
+      <c r="AE17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0</v>
       </c>
       <c r="AG17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI17" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AJ17" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK17" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL17" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM17" s="3">
-        <v>50</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AL17"/>
+      <c r="AM17"/>
       <c r="AN17"/>
       <c r="AO17"/>
       <c r="AP17"/>
       <c r="AQ17"/>
       <c r="AR17" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AS17" s="3">
-        <v>300</v>
-      </c>
-      <c r="AT17" s="3">
-        <v>3000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT17"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -2977,30 +3014,38 @@
       <c r="AY17"/>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A18"/>
+      <c r="A18" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B18" s="3">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D18"/>
-      <c r="E18"/>
+      <c r="E18" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
+      <c r="I18" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q18" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="R18" s="15" t="b">
         <v>0</v>
@@ -3011,126 +3056,144 @@
       <c r="V18"/>
       <c r="W18"/>
       <c r="X18"/>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18"/>
-      <c r="AB18"/>
+      <c r="Y18" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>300</v>
+      </c>
       <c r="AC18" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18"/>
-      <c r="AE18"/>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18"/>
+      <c r="AH18"/>
+      <c r="AI18"/>
       <c r="AJ18" s="3">
-        <v>15</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="3">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
       <c r="AN18"/>
       <c r="AO18"/>
       <c r="AP18"/>
       <c r="AQ18"/>
-      <c r="AR18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AS18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AT18" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AU18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
+      <c r="AU18" s="3">
+        <v>5</v>
+      </c>
       <c r="AV18"/>
       <c r="AW18"/>
       <c r="AX18"/>
       <c r="AY18"/>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A19"/>
+      <c r="A19" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B19" s="3">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D19"/>
       <c r="E19" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19"/>
+        <v>190</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="G19"/>
-      <c r="H19"/>
+      <c r="H19" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="I19" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K19"/>
       <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
+      <c r="M19" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="O19"/>
       <c r="P19" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R19" s="15" t="b">
         <v>0</v>
       </c>
       <c r="S19"/>
-      <c r="T19"/>
-      <c r="U19"/>
+      <c r="T19" s="3">
+        <v>1011</v>
+      </c>
+      <c r="U19" t="s">
+        <v>177</v>
+      </c>
       <c r="V19"/>
-      <c r="W19"/>
+      <c r="W19" t="s">
+        <v>183</v>
+      </c>
       <c r="X19"/>
       <c r="Y19" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Z19"/>
-      <c r="AA19"/>
-      <c r="AB19"/>
+        <v>20000</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>1000</v>
+      </c>
       <c r="AC19" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD19"/>
-      <c r="AE19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AJ19" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AK19" s="3">
         <v>10</v>
@@ -3142,7 +3205,7 @@
       <c r="AP19"/>
       <c r="AQ19"/>
       <c r="AR19" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AS19" s="3">
         <v>0</v>
@@ -3155,36 +3218,32 @@
       <c r="AY19"/>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A20"/>
+      <c r="A20" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="B20" s="3">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D20"/>
-      <c r="E20" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20"/>
-      <c r="I20" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>146</v>
-      </c>
+      <c r="I20"/>
+      <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
       <c r="O20"/>
       <c r="P20" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="R20" s="15" t="b">
         <v>0</v>
@@ -3195,158 +3254,140 @@
       <c r="V20"/>
       <c r="W20"/>
       <c r="X20"/>
-      <c r="Y20" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>300</v>
-      </c>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
       <c r="AC20" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20"/>
-      <c r="AE20" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG20"/>
-      <c r="AH20"/>
-      <c r="AI20"/>
+      <c r="AE20"/>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>160</v>
+      </c>
       <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK20"/>
+        <v>20</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>2</v>
+      </c>
       <c r="AL20"/>
       <c r="AM20"/>
       <c r="AN20"/>
       <c r="AO20"/>
       <c r="AP20"/>
       <c r="AQ20"/>
-      <c r="AR20"/>
-      <c r="AS20"/>
+      <c r="AR20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AS20" s="3">
+        <v>0</v>
+      </c>
       <c r="AT20"/>
-      <c r="AU20" s="3">
-        <v>5</v>
-      </c>
+      <c r="AU20"/>
       <c r="AV20"/>
-      <c r="AW20"/>
-      <c r="AX20"/>
-      <c r="AY20"/>
+      <c r="AW20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AX20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AY20" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21" s="3">
-        <v>1010</v>
+        <v>9001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21"/>
-      <c r="E21" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>192</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
       <c r="G21"/>
-      <c r="H21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>146</v>
-      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
-      <c r="M21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="M21"/>
+      <c r="N21"/>
       <c r="O21"/>
-      <c r="P21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>150</v>
+      <c r="P21"/>
+      <c r="Q21" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="R21" s="15" t="b">
         <v>0</v>
       </c>
       <c r="S21"/>
-      <c r="T21" s="3">
-        <v>1011</v>
-      </c>
-      <c r="U21" t="s">
-        <v>178</v>
-      </c>
+      <c r="T21"/>
+      <c r="U21"/>
       <c r="V21"/>
-      <c r="W21" t="s">
-        <v>184</v>
-      </c>
+      <c r="W21"/>
       <c r="X21"/>
       <c r="Y21" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>80</v>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="Z21"/>
       <c r="AA21" s="3">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AB21" s="3">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AC21" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="AD21" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI21" t="s">
+      <c r="AD21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="AG21"/>
+      <c r="AH21" s="3" t="s">
         <v>159</v>
       </c>
+      <c r="AI21" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="AJ21" s="3">
-        <v>50</v>
-      </c>
-      <c r="AK21" s="3">
-        <v>10</v>
-      </c>
-      <c r="AL21"/>
-      <c r="AM21"/>
+        <v>5</v>
+      </c>
+      <c r="AK21"/>
+      <c r="AL21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="3">
+        <v>2.5</v>
+      </c>
       <c r="AN21"/>
-      <c r="AO21"/>
+      <c r="AO21" s="3">
+        <v>2</v>
+      </c>
       <c r="AP21"/>
       <c r="AQ21"/>
-      <c r="AR21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AS21" s="3">
-        <v>0</v>
-      </c>
+      <c r="AR21"/>
+      <c r="AS21"/>
       <c r="AT21"/>
       <c r="AU21"/>
       <c r="AV21"/>
@@ -3357,15 +3398,19 @@
     <row r="22" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22" s="3">
-        <v>1011</v>
+        <v>9002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22"/>
+        <v>199</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
-      <c r="G22"/>
+      <c r="G22" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
@@ -3374,89 +3419,91 @@
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22"/>
-      <c r="P22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>150</v>
-      </c>
-      <c r="R22" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="P22"/>
+      <c r="Q22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22"/>
-      <c r="Y22"/>
+      <c r="Y22" s="3">
+        <v>4000</v>
+      </c>
       <c r="Z22"/>
-      <c r="AA22"/>
-      <c r="AB22"/>
+      <c r="AA22" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>300</v>
+      </c>
       <c r="AC22" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22"/>
-      <c r="AE22"/>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>159</v>
+        <v>1</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22"/>
+      <c r="AH22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="AJ22" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AK22" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL22"/>
       <c r="AM22"/>
-      <c r="AN22"/>
-      <c r="AO22"/>
+      <c r="AN22" s="3">
+        <v>12</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>12</v>
+      </c>
       <c r="AP22"/>
       <c r="AQ22"/>
-      <c r="AR22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AS22" s="3">
-        <v>0</v>
-      </c>
+      <c r="AR22"/>
+      <c r="AS22"/>
       <c r="AT22"/>
       <c r="AU22"/>
       <c r="AV22"/>
-      <c r="AW22" s="3">
-        <v>10</v>
-      </c>
-      <c r="AX22" s="3">
-        <v>10</v>
-      </c>
-      <c r="AY22" s="3">
-        <v>15</v>
-      </c>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A23"/>
       <c r="B23" s="3">
-        <v>9001</v>
+        <v>9101</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
+      <c r="H23" t="s">
+        <v>204</v>
+      </c>
+      <c r="I23" t="s">
+        <v>205</v>
+      </c>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -3465,11 +3512,9 @@
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="R23" s="15" t="b">
-        <v>0</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="R23"/>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
@@ -3477,47 +3522,47 @@
       <c r="W23"/>
       <c r="X23"/>
       <c r="Y23" s="3">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="Z23"/>
       <c r="AA23" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>350</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>250</v>
       </c>
       <c r="AC23" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD23" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE23" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF23" s="3">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="AG23"/>
       <c r="AH23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AJ23" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AK23"/>
       <c r="AL23" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM23" s="3">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AN23"/>
       <c r="AO23" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AP23"/>
       <c r="AQ23"/>
@@ -3533,21 +3578,23 @@
     <row r="24" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A24"/>
       <c r="B24" s="3">
-        <v>9002</v>
+        <v>9102</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
-      <c r="G24" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H24"/>
-      <c r="I24"/>
+      <c r="G24"/>
+      <c r="H24" t="s">
+        <v>208</v>
+      </c>
+      <c r="I24" t="s">
+        <v>209</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
@@ -3556,7 +3603,7 @@
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R24"/>
       <c r="S24"/>
@@ -3566,47 +3613,47 @@
       <c r="W24"/>
       <c r="X24"/>
       <c r="Y24" s="3">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="Z24"/>
       <c r="AA24" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AB24" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AC24" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AG24"/>
       <c r="AH24" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AJ24" s="3">
-        <v>8</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="AL24"/>
-      <c r="AM24"/>
-      <c r="AN24" s="3">
+        <v>22</v>
+      </c>
+      <c r="AK24"/>
+      <c r="AL24" s="3">
         <v>12</v>
       </c>
+      <c r="AM24" s="3">
+        <v>9</v>
+      </c>
+      <c r="AN24"/>
       <c r="AO24" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP24"/>
       <c r="AQ24"/>
@@ -3622,22 +3669,22 @@
     <row r="25" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A25"/>
       <c r="B25" s="3">
-        <v>9101</v>
+        <v>9103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I25" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
@@ -3647,7 +3694,7 @@
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R25"/>
       <c r="S25"/>
@@ -3655,55 +3702,65 @@
       <c r="U25"/>
       <c r="V25"/>
       <c r="W25"/>
-      <c r="X25"/>
+      <c r="X25">
+        <v>14</v>
+      </c>
       <c r="Y25" s="3">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="Z25"/>
       <c r="AA25" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB25" s="3">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="AC25" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD25" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="AF25" s="3">
-        <v>4</v>
-      </c>
-      <c r="AG25"/>
+        <v>12</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>158</v>
+      </c>
       <c r="AH25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AJ25" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK25"/>
       <c r="AL25" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AM25" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AN25"/>
       <c r="AO25" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AP25"/>
       <c r="AQ25"/>
-      <c r="AR25"/>
-      <c r="AS25"/>
-      <c r="AT25"/>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>400</v>
+      </c>
+      <c r="AT25">
+        <v>2000</v>
+      </c>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -3713,22 +3770,22 @@
     <row r="26" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A26"/>
       <c r="B26" s="3">
-        <v>9102</v>
+        <v>9104</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I26" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
@@ -3738,7 +3795,7 @@
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R26"/>
       <c r="S26"/>
@@ -3748,47 +3805,47 @@
       <c r="W26"/>
       <c r="X26"/>
       <c r="Y26" s="3">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="Z26"/>
       <c r="AA26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB26" s="3">
         <v>900</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>700</v>
       </c>
       <c r="AC26" s="15" t="b">
         <v>1</v>
       </c>
       <c r="AD26" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF26" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="AG26"/>
+        <v>0</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>158</v>
+      </c>
       <c r="AH26" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AI26" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AJ26" s="3">
-        <v>22</v>
-      </c>
-      <c r="AK26"/>
-      <c r="AL26" s="3">
-        <v>12</v>
-      </c>
-      <c r="AM26" s="3">
-        <v>9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="AK26">
+        <v>14</v>
+      </c>
+      <c r="AL26"/>
+      <c r="AM26"/>
       <c r="AN26"/>
       <c r="AO26" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP26"/>
       <c r="AQ26"/>
@@ -3803,195 +3860,397 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A27"/>
-      <c r="B27" s="3">
-        <v>9103</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>212</v>
+      <c r="B27">
+        <v>2001</v>
+      </c>
+      <c r="C27" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" t="s">
+        <v>219</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I27" t="s">
-        <v>214</v>
-      </c>
-      <c r="J27"/>
+        <v>221</v>
+      </c>
       <c r="K27"/>
       <c r="L27"/>
       <c r="M27"/>
       <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>222</v>
+      </c>
       <c r="Q27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
+        <v>151</v>
+      </c>
+      <c r="R27" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
       <c r="U27"/>
-      <c r="V27"/>
+      <c r="V27">
+        <v>0</v>
+      </c>
       <c r="W27"/>
       <c r="X27">
-        <v>14</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>14000</v>
-      </c>
-      <c r="Z27"/>
-      <c r="AA27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC27" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>600</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>400</v>
+      </c>
+      <c r="AB27">
+        <v>500</v>
+      </c>
+      <c r="AC27" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE27" s="3" t="s">
+      <c r="AD27" t="s">
         <v>152</v>
       </c>
-      <c r="AF27" s="3">
-        <v>12</v>
+      <c r="AE27" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
       </c>
       <c r="AG27" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH27" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AH27" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ27">
+        <v>50</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>10</v>
+      </c>
+      <c r="AM27">
+        <v>10</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
         <v>8</v>
       </c>
-      <c r="AK27"/>
-      <c r="AL27" s="3">
-        <v>8</v>
-      </c>
-      <c r="AM27" s="3">
-        <v>24</v>
-      </c>
-      <c r="AN27"/>
-      <c r="AO27" s="3">
-        <v>24</v>
-      </c>
-      <c r="AP27"/>
-      <c r="AQ27"/>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
       <c r="AR27">
         <v>0</v>
       </c>
       <c r="AS27">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2000</v>
-      </c>
-      <c r="AU27"/>
-      <c r="AV27"/>
-      <c r="AW27"/>
-      <c r="AX27"/>
-      <c r="AY27"/>
+        <v>600</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A28"/>
-      <c r="B28" s="3">
-        <v>9104</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>216</v>
+      <c r="B28">
+        <v>2002</v>
+      </c>
+      <c r="C28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" t="s">
+        <v>224</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I28" t="s">
-        <v>218</v>
-      </c>
-      <c r="J28"/>
+        <v>226</v>
+      </c>
       <c r="K28"/>
       <c r="L28"/>
       <c r="M28"/>
       <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28" t="s">
+        <v>222</v>
+      </c>
       <c r="Q28" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="T28"/>
+        <v>151</v>
+      </c>
+      <c r="R28" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28"/>
-      <c r="V28"/>
+      <c r="V28">
+        <v>0</v>
+      </c>
       <c r="W28"/>
-      <c r="X28"/>
-      <c r="Y28" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z28"/>
-      <c r="AA28" s="3">
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>2500</v>
+      </c>
+      <c r="Z28">
+        <v>10</v>
+      </c>
+      <c r="AA28">
         <v>1200</v>
       </c>
-      <c r="AB28" s="3">
-        <v>900</v>
-      </c>
-      <c r="AC28" s="15" t="b">
+      <c r="AB28">
+        <v>1500</v>
+      </c>
+      <c r="AC28" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AD28" s="3" t="s">
+      <c r="AD28" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF28">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ28">
+        <v>100</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>18</v>
+      </c>
+      <c r="AM28">
+        <v>12</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>12</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>1000</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A29"/>
+      <c r="B29">
+        <v>2003</v>
+      </c>
+      <c r="C29" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29" t="s">
+        <v>229</v>
+      </c>
+      <c r="I29" t="s">
+        <v>221</v>
+      </c>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AE28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH28" s="3" t="s">
+      <c r="R29" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29"/>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29"/>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>4000</v>
+      </c>
+      <c r="Z29">
+        <v>15</v>
+      </c>
+      <c r="AA29">
+        <v>400</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD29"/>
+      <c r="AE29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="s">
         <v>158</v>
       </c>
-      <c r="AI28" s="3" t="s">
+      <c r="AH29" t="s">
         <v>159</v>
       </c>
-      <c r="AJ28" s="3">
-        <v>15</v>
-      </c>
-      <c r="AK28">
-        <v>14</v>
-      </c>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28" s="3">
-        <v>14</v>
-      </c>
-      <c r="AP28"/>
-      <c r="AQ28"/>
-      <c r="AR28"/>
-      <c r="AS28"/>
-      <c r="AT28"/>
-      <c r="AU28"/>
-      <c r="AV28"/>
-      <c r="AW28"/>
-      <c r="AX28"/>
-      <c r="AY28"/>
+      <c r="AI29" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ29">
+        <v>30</v>
+      </c>
+      <c r="AK29">
+        <v>5</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>5</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>250</v>
+      </c>
+      <c r="AT29">
+        <v>1000</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F07CAE3-2963-4035-A248-4D60436322DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5DD251-2224-45A3-980A-14B593A628CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="231">
   <si>
     <t>데이터이름</t>
   </si>
@@ -628,30 +628,6 @@
     <t>Art/GabrielAguiarProductions_Projectile/UniqueProjectilesVol_4/Prefabs/Projectiles/vfx_Projectile_Arrow06</t>
   </si>
   <si>
-    <t>Dragon_Bite</t>
-  </si>
-  <si>
-    <t>드래곤 물기(잔기술). 짧은 윈드업, 짧은 쿨</t>
-  </si>
-  <si>
-    <t>Art/DragonVFX/FX_FireHit_02</t>
-  </si>
-  <si>
-    <t>Bite</t>
-  </si>
-  <si>
-    <t>Dragon_ClawSweep</t>
-  </si>
-  <si>
-    <t>드래곤 할퀴기(전방 광역). 긴 윈드업 = 회피 가능</t>
-  </si>
-  <si>
-    <t>Art/DragonVFX/DragonClawSlash</t>
-  </si>
-  <si>
-    <t>ClawSweep</t>
-  </si>
-  <si>
     <t>Dragon_FlameBreath</t>
   </si>
   <si>
@@ -664,52 +640,88 @@
     <t>FlameBreath</t>
   </si>
   <si>
-    <t>Dragon_Roar</t>
-  </si>
-  <si>
-    <t>드래곤 포효. 자기중심 광역. 최우선(쿨 길어 가끔)</t>
-  </si>
-  <si>
-    <t>Art/DragonVFX/FX_Fire_CircleShock</t>
+    <t>Warrior_NarrowSlash</t>
+  </si>
+  <si>
+    <t>전사 전방 좁은 범위 1회 즉발 공격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/NarrowSlash</t>
+  </si>
+  <si>
+    <t>Melee_1</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Warrior_WideSlash</t>
+  </si>
+  <si>
+    <t>전사 전방 넓은 범위 1회 즉발 공격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/WideSlash</t>
+  </si>
+  <si>
+    <t>Melee_2</t>
+  </si>
+  <si>
+    <t>Warrior_MultiSlash</t>
+  </si>
+  <si>
+    <t>전사 캐릭터 주변 좁은 범위 빠른 5회 타격</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Warrior/MultiSlash</t>
+  </si>
+  <si>
+    <t>ProjectilePierce</t>
+  </si>
+  <si>
+    <t>Dragon_GodCall</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonGodCall</t>
   </si>
   <si>
     <t>Roar</t>
   </si>
   <si>
-    <t>Warrior_NarrowSlash</t>
-  </si>
-  <si>
-    <t>전사 전방 좁은 범위 1회 즉발 공격</t>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Warrior/NarrowSlash</t>
-  </si>
-  <si>
-    <t>Melee_1</t>
-  </si>
-  <si>
-    <t>Warrior</t>
-  </si>
-  <si>
-    <t>Warrior_WideSlash</t>
-  </si>
-  <si>
-    <t>전사 전방 넓은 범위 1회 즉발 공격</t>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Warrior/WideSlash</t>
-  </si>
-  <si>
-    <t>Melee_2</t>
-  </si>
-  <si>
-    <t>Warrior_MultiSlash</t>
-  </si>
-  <si>
-    <t>전사 캐릭터 주변 좁은 범위 빠른 5회 타격</t>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Warrior/MultiSlash</t>
+    <t>투사체 관통 여부</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체일 경우 true면 대상/지형 충돌로 소멸하지 않고 최대사거리까지 이동</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonBullet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dragon_ShockWave</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dragon_Bullet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방으로 5개의 관통 투사체를 발사한다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방으로 1개의 관통 투사체를 발사한다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonShockWave</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변 무작위 영역 10곳을 각각 1회 타격한다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -851,7 +863,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -916,6 +928,12 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1148,12 +1166,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
-    <col min="3" max="4" width="19.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="3" customWidth="1"/>
     <col min="5" max="5" width="22" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="63.125" style="3" customWidth="1"/>
@@ -1171,14 +1190,14 @@
     <col min="25" max="25" width="20.875" style="3" customWidth="1"/>
     <col min="26" max="31" width="18.25" style="3" customWidth="1"/>
     <col min="32" max="32" width="24" style="3" customWidth="1"/>
-    <col min="33" max="38" width="18.25" style="3" customWidth="1"/>
-    <col min="39" max="39" width="20.75" style="3" customWidth="1"/>
-    <col min="40" max="51" width="18.25" style="3" customWidth="1"/>
-    <col min="52" max="53" width="9" style="3" customWidth="1"/>
+    <col min="33" max="39" width="18.25" style="3" customWidth="1"/>
+    <col min="40" max="40" width="20.75" style="3" customWidth="1"/>
+    <col min="41" max="52" width="18.25" style="3" customWidth="1"/>
+    <col min="53" max="53" width="9" style="3" customWidth="1"/>
     <col min="54" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,8 +1253,9 @@
       <c r="AW1"/>
       <c r="AX1"/>
       <c r="AY1"/>
+      <c r="AZ1"/>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1334,55 +1354,58 @@
         <v>30</v>
       </c>
       <c r="AJ2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AL2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AM2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AO2" s="4" t="s">
+      <c r="AP2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AP2" s="4" t="s">
+      <c r="AQ2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AQ2" s="4" t="s">
+      <c r="AR2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AR2" s="4" t="s">
+      <c r="AS2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AS2" s="4" t="s">
+      <c r="AT2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AT2" s="4" t="s">
+      <c r="AU2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AU2" s="4" t="s">
+      <c r="AV2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AV2" s="4" t="s">
+      <c r="AW2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AW2" s="4" t="s">
+      <c r="AX2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="AX2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="AY2" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="AZ2" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="3" spans="1:51" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>46</v>
       </c>
@@ -1464,7 +1487,9 @@
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
+      <c r="AJ3" s="16" t="s">
+        <v>223</v>
+      </c>
       <c r="AK3" s="6"/>
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
@@ -1473,23 +1498,24 @@
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
       <c r="AR3" s="6"/>
-      <c r="AS3" s="6" t="s">
+      <c r="AS3" s="6"/>
+      <c r="AT3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
-      <c r="AW3" s="6" t="s">
+      <c r="AW3" s="6"/>
+      <c r="AX3" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="AX3" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="AY3" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="AZ3" s="6" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1643,8 +1669,11 @@
       <c r="AY4" s="8" t="s">
         <v>72</v>
       </c>
+      <c r="AZ4" s="8" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
@@ -1749,10 +1778,10 @@
         <v>78</v>
       </c>
       <c r="AJ5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK5" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="AK5" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="AL5" s="8" t="s">
         <v>80</v>
@@ -1767,13 +1796,13 @@
         <v>80</v>
       </c>
       <c r="AP5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="AQ5" s="8" t="s">
+      <c r="AR5" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="AR5" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="AS5" s="8" t="s">
         <v>76</v>
@@ -1782,22 +1811,25 @@
         <v>76</v>
       </c>
       <c r="AU5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AV5" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="AV5" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="AW5" s="8" t="s">
         <v>76</v>
       </c>
       <c r="AX5" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AY5" s="8" t="s">
         <v>80</v>
       </c>
+      <c r="AZ5" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
@@ -1869,8 +1901,9 @@
       <c r="AW6" s="8"/>
       <c r="AX6" s="8"/>
       <c r="AY6" s="8"/>
+      <c r="AZ6" s="8"/>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -1932,7 +1965,7 @@
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
-      <c r="AJ7" s="8">
+      <c r="AJ7" s="8" t="b">
         <v>0</v>
       </c>
       <c r="AK7" s="8">
@@ -1980,8 +2013,11 @@
       <c r="AY7" s="8">
         <v>0</v>
       </c>
+      <c r="AZ7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:51" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>93</v>
       </c>
@@ -2088,55 +2124,58 @@
         <v>126</v>
       </c>
       <c r="AJ8" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="AK8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="AK8" s="10" t="s">
+      <c r="AL8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AL8" s="10" t="s">
+      <c r="AM8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AM8" s="10" t="s">
+      <c r="AN8" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AN8" s="10" t="s">
+      <c r="AO8" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AO8" s="10" t="s">
+      <c r="AP8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AP8" s="10" t="s">
+      <c r="AQ8" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AQ8" s="10" t="s">
+      <c r="AR8" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="AR8" s="10" t="s">
+      <c r="AS8" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="AS8" s="10" t="s">
+      <c r="AT8" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="AT8" s="10" t="s">
+      <c r="AU8" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="AU8" s="10" t="s">
+      <c r="AV8" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AV8" s="10" t="s">
+      <c r="AW8" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="AW8" s="10" t="s">
+      <c r="AX8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="AX8" s="10" t="s">
+      <c r="AY8" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="AY8" s="10" t="s">
+      <c r="AZ8" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9" s="3">
         <v>1001</v>
@@ -2216,25 +2255,25 @@
         <v>155</v>
       </c>
       <c r="AI9"/>
-      <c r="AJ9" s="3">
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="3">
         <v>50</v>
       </c>
-      <c r="AK9"/>
       <c r="AL9"/>
       <c r="AM9"/>
-      <c r="AN9" s="3">
-        <v>15</v>
-      </c>
+      <c r="AN9"/>
       <c r="AO9" s="3">
         <v>15</v>
       </c>
       <c r="AP9" s="3">
+        <v>15</v>
+      </c>
+      <c r="AQ9" s="3">
         <v>5</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AR9" s="3">
         <v>90</v>
       </c>
-      <c r="AR9"/>
       <c r="AS9"/>
       <c r="AT9"/>
       <c r="AU9"/>
@@ -2242,8 +2281,9 @@
       <c r="AW9"/>
       <c r="AX9"/>
       <c r="AY9"/>
+      <c r="AZ9"/>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A10"/>
       <c r="B10" s="3">
         <v>1002</v>
@@ -2301,13 +2341,13 @@
       <c r="AI10" t="s">
         <v>160</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="3">
         <v>30</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5</v>
       </c>
-      <c r="AL10"/>
       <c r="AM10"/>
       <c r="AN10"/>
       <c r="AO10"/>
@@ -2321,8 +2361,9 @@
       <c r="AW10"/>
       <c r="AX10"/>
       <c r="AY10"/>
+      <c r="AZ10"/>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A11"/>
       <c r="B11" s="3">
         <v>1003</v>
@@ -2404,36 +2445,37 @@
       <c r="AI11" t="s">
         <v>167</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="3">
         <v>15</v>
       </c>
-      <c r="AK11"/>
-      <c r="AL11" s="3">
-        <v>10</v>
-      </c>
+      <c r="AL11"/>
       <c r="AM11" s="3">
         <v>10</v>
       </c>
-      <c r="AN11"/>
+      <c r="AN11" s="3">
+        <v>10</v>
+      </c>
       <c r="AO11"/>
       <c r="AP11"/>
       <c r="AQ11"/>
-      <c r="AR11" s="3">
-        <v>0</v>
-      </c>
+      <c r="AR11"/>
       <c r="AS11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="3">
         <v>1000</v>
       </c>
-      <c r="AT11" s="3">
+      <c r="AU11" s="3">
         <v>2000</v>
       </c>
-      <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
       <c r="AX11"/>
       <c r="AY11"/>
+      <c r="AZ11"/>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A12"/>
       <c r="B12" s="3">
         <v>1008</v>
@@ -2513,36 +2555,37 @@
       <c r="AI12" t="s">
         <v>167</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="3">
         <v>40</v>
       </c>
-      <c r="AK12"/>
-      <c r="AL12" s="3">
-        <v>20</v>
-      </c>
+      <c r="AL12"/>
       <c r="AM12" s="3">
         <v>20</v>
       </c>
-      <c r="AN12"/>
+      <c r="AN12" s="3">
+        <v>20</v>
+      </c>
       <c r="AO12"/>
       <c r="AP12"/>
       <c r="AQ12"/>
-      <c r="AR12" s="3">
-        <v>0</v>
-      </c>
+      <c r="AR12"/>
       <c r="AS12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="3">
         <v>1000</v>
       </c>
-      <c r="AT12" s="3">
+      <c r="AU12" s="3">
         <v>5000</v>
       </c>
-      <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
       <c r="AX12"/>
       <c r="AY12"/>
+      <c r="AZ12"/>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>173</v>
       </c>
@@ -2616,10 +2659,10 @@
       <c r="AG13"/>
       <c r="AH13"/>
       <c r="AI13"/>
-      <c r="AJ13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK13"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
@@ -2629,17 +2672,18 @@
       <c r="AR13"/>
       <c r="AS13"/>
       <c r="AT13"/>
-      <c r="AU13" s="3">
+      <c r="AU13"/>
+      <c r="AV13" s="3">
         <v>10</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="AW13" s="3">
         <v>1000</v>
       </c>
-      <c r="AW13"/>
       <c r="AX13"/>
       <c r="AY13"/>
+      <c r="AZ13"/>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>173</v>
       </c>
@@ -2697,13 +2741,13 @@
       <c r="AI14" t="s">
         <v>160</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="19"/>
+      <c r="AK14" s="3">
         <v>20</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>3</v>
       </c>
-      <c r="AL14"/>
       <c r="AM14"/>
       <c r="AN14"/>
       <c r="AO14"/>
@@ -2717,8 +2761,9 @@
       <c r="AW14"/>
       <c r="AX14"/>
       <c r="AY14"/>
+      <c r="AZ14"/>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>173</v>
       </c>
@@ -2800,38 +2845,39 @@
       <c r="AI15" t="s">
         <v>167</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="3">
         <v>40</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>5</v>
       </c>
       <c r="AL15" s="3">
         <v>5</v>
       </c>
       <c r="AM15" s="3">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="3">
         <v>50</v>
       </c>
-      <c r="AN15"/>
       <c r="AO15"/>
       <c r="AP15"/>
       <c r="AQ15"/>
-      <c r="AR15" s="3">
-        <v>0</v>
-      </c>
+      <c r="AR15"/>
       <c r="AS15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="3">
         <v>300</v>
       </c>
-      <c r="AT15" s="3">
+      <c r="AU15" s="3">
         <v>3000</v>
       </c>
-      <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
       <c r="AX15"/>
       <c r="AY15"/>
+      <c r="AZ15"/>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>173</v>
       </c>
@@ -2889,38 +2935,39 @@
       <c r="AI16" t="s">
         <v>167</v>
       </c>
-      <c r="AJ16" s="3">
+      <c r="AJ16" s="19"/>
+      <c r="AK16" s="3">
         <v>15</v>
-      </c>
-      <c r="AK16" s="3">
-        <v>5</v>
       </c>
       <c r="AL16" s="3">
         <v>5</v>
       </c>
       <c r="AM16" s="3">
+        <v>5</v>
+      </c>
+      <c r="AN16" s="3">
         <v>50</v>
       </c>
-      <c r="AN16"/>
       <c r="AO16"/>
       <c r="AP16"/>
       <c r="AQ16"/>
-      <c r="AR16" s="3">
-        <v>1000</v>
-      </c>
+      <c r="AR16"/>
       <c r="AS16" s="3">
         <v>1000</v>
       </c>
       <c r="AT16" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AU16" s="3">
         <v>5000</v>
       </c>
-      <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
       <c r="AX16"/>
       <c r="AY16"/>
+      <c r="AZ16"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>173</v>
       </c>
@@ -2988,32 +3035,33 @@
       <c r="AI17" t="s">
         <v>160</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="19"/>
+      <c r="AK17" s="3">
         <v>30</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>10</v>
       </c>
-      <c r="AL17"/>
       <c r="AM17"/>
       <c r="AN17"/>
       <c r="AO17"/>
       <c r="AP17"/>
       <c r="AQ17"/>
-      <c r="AR17" s="3">
+      <c r="AR17"/>
+      <c r="AS17" s="3">
         <v>300</v>
       </c>
-      <c r="AS17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT17"/>
+      <c r="AT17" s="3">
+        <v>0</v>
+      </c>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
       <c r="AX17"/>
       <c r="AY17"/>
+      <c r="AZ17"/>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>173</v>
       </c>
@@ -3081,10 +3129,10 @@
       <c r="AG18"/>
       <c r="AH18"/>
       <c r="AI18"/>
-      <c r="AJ18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK18"/>
+      <c r="AJ18" s="19"/>
+      <c r="AK18" s="3">
+        <v>0</v>
+      </c>
       <c r="AL18"/>
       <c r="AM18"/>
       <c r="AN18"/>
@@ -3094,15 +3142,16 @@
       <c r="AR18"/>
       <c r="AS18"/>
       <c r="AT18"/>
-      <c r="AU18" s="3">
+      <c r="AU18"/>
+      <c r="AV18" s="3">
         <v>5</v>
       </c>
-      <c r="AV18"/>
       <c r="AW18"/>
       <c r="AX18"/>
       <c r="AY18"/>
+      <c r="AZ18"/>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>173</v>
       </c>
@@ -3192,32 +3241,33 @@
       <c r="AI19" t="s">
         <v>160</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AJ19" s="19"/>
+      <c r="AK19" s="3">
         <v>50</v>
       </c>
-      <c r="AK19" s="3">
+      <c r="AL19" s="3">
         <v>10</v>
       </c>
-      <c r="AL19"/>
       <c r="AM19"/>
       <c r="AN19"/>
       <c r="AO19"/>
       <c r="AP19"/>
       <c r="AQ19"/>
-      <c r="AR19" s="3">
+      <c r="AR19"/>
+      <c r="AS19" s="3">
         <v>1000</v>
       </c>
-      <c r="AS19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT19"/>
+      <c r="AT19" s="3">
+        <v>0</v>
+      </c>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
       <c r="AX19"/>
       <c r="AY19"/>
+      <c r="AZ19"/>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>173</v>
       </c>
@@ -3275,38 +3325,39 @@
       <c r="AI20" t="s">
         <v>160</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="3">
         <v>20</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2</v>
       </c>
-      <c r="AL20"/>
       <c r="AM20"/>
       <c r="AN20"/>
       <c r="AO20"/>
       <c r="AP20"/>
       <c r="AQ20"/>
-      <c r="AR20" s="3">
+      <c r="AR20"/>
+      <c r="AS20" s="3">
         <v>1000</v>
       </c>
-      <c r="AS20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT20"/>
+      <c r="AT20" s="3">
+        <v>0</v>
+      </c>
       <c r="AU20"/>
       <c r="AV20"/>
-      <c r="AW20" s="3">
-        <v>10</v>
-      </c>
+      <c r="AW20"/>
       <c r="AX20" s="3">
         <v>10</v>
       </c>
       <c r="AY20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AZ20" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21" s="3">
         <v>9001</v>
@@ -3370,21 +3421,20 @@
       <c r="AI21" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5</v>
       </c>
-      <c r="AK21"/>
-      <c r="AL21" s="3">
+      <c r="AL21"/>
+      <c r="AM21" s="3">
         <v>2</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2.5</v>
       </c>
-      <c r="AN21"/>
-      <c r="AO21" s="3">
+      <c r="AO21"/>
+      <c r="AP21" s="3">
         <v>2</v>
       </c>
-      <c r="AP21"/>
       <c r="AQ21"/>
       <c r="AR21"/>
       <c r="AS21"/>
@@ -3394,8 +3444,9 @@
       <c r="AW21"/>
       <c r="AX21"/>
       <c r="AY21"/>
+      <c r="AZ21"/>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22" s="3">
         <v>9002</v>
@@ -3459,21 +3510,20 @@
       <c r="AI22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1.5</v>
       </c>
-      <c r="AL22"/>
       <c r="AM22"/>
-      <c r="AN22" s="3">
-        <v>12</v>
-      </c>
+      <c r="AN22"/>
       <c r="AO22" s="3">
         <v>12</v>
       </c>
-      <c r="AP22"/>
+      <c r="AP22" s="3">
+        <v>12</v>
+      </c>
       <c r="AQ22"/>
       <c r="AR22"/>
       <c r="AS22"/>
@@ -3483,24 +3533,25 @@
       <c r="AW22"/>
       <c r="AX22"/>
       <c r="AY22"/>
+      <c r="AZ22"/>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A23"/>
       <c r="B23" s="3">
         <v>9101</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>203</v>
+      <c r="C23" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>227</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23" t="s">
-        <v>204</v>
-      </c>
+      <c r="G23" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="H23"/>
       <c r="I23" t="s">
         <v>205</v>
       </c>
@@ -3538,62 +3589,81 @@
         <v>152</v>
       </c>
       <c r="AE23" s="3" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AF23" s="3">
-        <v>4</v>
-      </c>
-      <c r="AG23"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>154</v>
+      </c>
       <c r="AH23" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ23" s="3">
+        <v>160</v>
+      </c>
+      <c r="AJ23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK23" s="3">
         <v>12</v>
       </c>
-      <c r="AK23"/>
-      <c r="AL23" s="3">
-        <v>4</v>
+      <c r="AL23">
+        <v>3</v>
       </c>
       <c r="AM23" s="3">
-        <v>8</v>
-      </c>
-      <c r="AN23"/>
-      <c r="AO23" s="3">
-        <v>8</v>
-      </c>
-      <c r="AP23"/>
-      <c r="AQ23"/>
-      <c r="AR23"/>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>15</v>
+      </c>
+      <c r="AP23" s="3">
+        <v>30</v>
+      </c>
+      <c r="AQ23">
+        <v>5</v>
+      </c>
+      <c r="AR23">
+        <v>90</v>
+      </c>
       <c r="AS23"/>
       <c r="AT23"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
-      <c r="AX23"/>
-      <c r="AY23"/>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A24"/>
       <c r="B24" s="3">
         <v>9102</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>207</v>
+        <v>219</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="I24" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
@@ -3632,59 +3702,81 @@
         <v>179</v>
       </c>
       <c r="AF24" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="AG24"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>158</v>
+      </c>
       <c r="AH24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ24" s="3">
+        <v>160</v>
+      </c>
+      <c r="AK24" s="3">
         <v>22</v>
       </c>
-      <c r="AK24"/>
-      <c r="AL24" s="3">
-        <v>12</v>
+      <c r="AL24">
+        <v>5</v>
       </c>
       <c r="AM24" s="3">
-        <v>9</v>
-      </c>
-      <c r="AN24"/>
-      <c r="AO24" s="3">
-        <v>9</v>
-      </c>
-      <c r="AP24"/>
-      <c r="AQ24"/>
-      <c r="AR24"/>
-      <c r="AS24"/>
-      <c r="AT24"/>
-      <c r="AU24"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>20</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>1500</v>
+      </c>
       <c r="AV24"/>
       <c r="AW24"/>
-      <c r="AX24"/>
-      <c r="AY24"/>
+      <c r="AX24">
+        <v>20</v>
+      </c>
+      <c r="AY24">
+        <v>15</v>
+      </c>
+      <c r="AZ24">
+        <v>30</v>
+      </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A25"/>
       <c r="B25" s="3">
         <v>9103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I25" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
@@ -3736,56 +3828,56 @@
       <c r="AI25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AJ25" s="3">
+      <c r="AK25" s="3">
         <v>8</v>
       </c>
-      <c r="AK25"/>
-      <c r="AL25" s="3">
+      <c r="AL25"/>
+      <c r="AM25" s="3">
         <v>8</v>
       </c>
-      <c r="AM25" s="3">
+      <c r="AN25" s="3">
         <v>24</v>
       </c>
-      <c r="AN25"/>
-      <c r="AO25" s="3">
+      <c r="AO25"/>
+      <c r="AP25" s="3">
         <v>24</v>
       </c>
-      <c r="AP25"/>
       <c r="AQ25"/>
-      <c r="AR25">
-        <v>0</v>
-      </c>
+      <c r="AR25"/>
       <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
         <v>400</v>
       </c>
-      <c r="AT25">
+      <c r="AU25">
         <v>2000</v>
       </c>
-      <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
       <c r="AX25"/>
       <c r="AY25"/>
+      <c r="AZ25"/>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A26"/>
       <c r="B26" s="3">
         <v>9104</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>215</v>
+      <c r="C26" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26" t="s">
-        <v>216</v>
-      </c>
+      <c r="G26" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="H26" s="17"/>
       <c r="I26" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
@@ -3805,14 +3897,14 @@
       <c r="W26"/>
       <c r="X26"/>
       <c r="Y26" s="3">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="Z26"/>
       <c r="AA26" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AB26" s="3">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="AC26" s="15" t="b">
         <v>1</v>
@@ -3821,35 +3913,43 @@
         <v>152</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
       <c r="AG26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AH26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>15</v>
-      </c>
-      <c r="AK26">
-        <v>14</v>
-      </c>
-      <c r="AL26"/>
+      <c r="AJ26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>30</v>
+      </c>
+      <c r="AL26">
+        <v>10</v>
+      </c>
       <c r="AM26"/>
       <c r="AN26"/>
-      <c r="AO26" s="3">
-        <v>14</v>
-      </c>
-      <c r="AP26"/>
-      <c r="AQ26"/>
-      <c r="AR26"/>
+      <c r="AO26">
+        <v>12</v>
+      </c>
+      <c r="AP26" s="3">
+        <v>30</v>
+      </c>
+      <c r="AQ26">
+        <v>1</v>
+      </c>
+      <c r="AR26">
+        <v>90</v>
+      </c>
       <c r="AS26"/>
       <c r="AT26"/>
       <c r="AU26"/>
@@ -3857,26 +3957,27 @@
       <c r="AW26"/>
       <c r="AX26"/>
       <c r="AY26"/>
+      <c r="AZ26"/>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A27"/>
-      <c r="B27">
+      <c r="B27" s="19">
         <v>2001</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="I27" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="K27"/>
       <c r="L27"/>
@@ -3886,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>151</v>
@@ -3941,27 +4042,25 @@
       <c r="AI27" t="s">
         <v>167</v>
       </c>
-      <c r="AJ27">
+      <c r="AJ27" s="19"/>
+      <c r="AK27">
         <v>50</v>
       </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
       <c r="AL27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM27">
         <v>10</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
         <v>8</v>
       </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
       <c r="AQ27">
         <v>0</v>
       </c>
@@ -3972,11 +4071,11 @@
         <v>0</v>
       </c>
       <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
         <v>600</v>
       </c>
-      <c r="AU27">
-        <v>0</v>
-      </c>
       <c r="AV27">
         <v>0</v>
       </c>
@@ -3989,26 +4088,29 @@
       <c r="AY27">
         <v>0</v>
       </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A28"/>
-      <c r="B28">
+      <c r="B28" s="19">
         <v>2002</v>
       </c>
       <c r="C28" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="I28" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="K28"/>
       <c r="L28"/>
@@ -4018,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>151</v>
@@ -4073,27 +4175,25 @@
       <c r="AI28" t="s">
         <v>167</v>
       </c>
-      <c r="AJ28">
+      <c r="AJ28" s="19"/>
+      <c r="AK28">
         <v>100</v>
       </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
       <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
         <v>18</v>
       </c>
-      <c r="AM28">
+      <c r="AN28">
         <v>12</v>
       </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
       <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
         <v>12</v>
       </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
       <c r="AQ28">
         <v>0</v>
       </c>
@@ -4104,11 +4204,11 @@
         <v>0</v>
       </c>
       <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
         <v>1000</v>
       </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
       <c r="AV28">
         <v>0</v>
       </c>
@@ -4121,26 +4221,29 @@
       <c r="AY28">
         <v>0</v>
       </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A29"/>
-      <c r="B29">
+      <c r="B29" s="19">
         <v>2003</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D29" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I29" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="K29"/>
       <c r="L29"/>
@@ -4150,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>151</v>
@@ -4203,15 +4306,13 @@
       <c r="AI29" t="s">
         <v>160</v>
       </c>
-      <c r="AJ29">
+      <c r="AJ29" s="19"/>
+      <c r="AK29">
         <v>30</v>
       </c>
-      <c r="AK29">
+      <c r="AL29">
         <v>5</v>
       </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
       <c r="AM29">
         <v>0</v>
       </c>
@@ -4219,11 +4320,11 @@
         <v>0</v>
       </c>
       <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
         <v>5</v>
       </c>
-      <c r="AP29">
-        <v>0</v>
-      </c>
       <c r="AQ29">
         <v>0</v>
       </c>
@@ -4231,14 +4332,14 @@
         <v>0</v>
       </c>
       <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
         <v>250</v>
       </c>
-      <c r="AT29">
+      <c r="AU29">
         <v>1000</v>
       </c>
-      <c r="AU29">
-        <v>0</v>
-      </c>
       <c r="AV29">
         <v>0</v>
       </c>
@@ -4249,6 +4350,9 @@
         <v>0</v>
       </c>
       <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
         <v>0</v>
       </c>
     </row>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5DD251-2224-45A3-980A-14B593A628CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC838415-4E73-4AB6-ADB1-E7BEE75D50B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="234">
   <si>
     <t>데이터이름</t>
   </si>
@@ -115,6 +115,9 @@
     <t>스킬 효과 모양</t>
   </si>
   <si>
+    <t>투사체 관통 여부</t>
+  </si>
+  <si>
     <t>대미지 계수</t>
   </si>
   <si>
@@ -226,6 +229,9 @@
     <t>Placement 기준점에서 효과 중심까지의 전방 거리. 예를들면 빔의 시작점을 SkillCastOrigin에 맞추려면 ObbLength의 절반을 입력한다.</t>
   </si>
   <si>
+    <t>투사체일 경우 true면 대상/지형 충돌로 소멸하지 않고 최대사거리까지 이동</t>
+  </si>
+  <si>
     <t>0이면 단일 틱=instant</t>
   </si>
   <si>
@@ -403,6 +409,9 @@
     <t>EffectShape</t>
   </si>
   <si>
+    <t>ProjectilePierce</t>
+  </si>
+  <si>
     <t>DamageCoeff</t>
   </si>
   <si>
@@ -628,6 +637,30 @@
     <t>Art/GabrielAguiarProductions_Projectile/UniqueProjectilesVol_4/Prefabs/Projectiles/vfx_Projectile_Arrow06</t>
   </si>
   <si>
+    <t>Dragon_Bullet</t>
+  </si>
+  <si>
+    <t>전방으로 5개의 관통 투사체를 발사한다.</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonBullet</t>
+  </si>
+  <si>
+    <t>FlameBreath</t>
+  </si>
+  <si>
+    <t>Dragon_GodCall</t>
+  </si>
+  <si>
+    <t>주변 무작위 영역 10곳을 각각 1회 타격한다.</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonCartoonLightning</t>
+  </si>
+  <si>
+    <t>Roar</t>
+  </si>
+  <si>
     <t>Dragon_FlameBreath</t>
   </si>
   <si>
@@ -637,7 +670,13 @@
     <t>Art/DragonVFX/FX_Dragonfire</t>
   </si>
   <si>
-    <t>FlameBreath</t>
+    <t>Dragon_ShockWave</t>
+  </si>
+  <si>
+    <t>전방으로 1개의 관통 투사체를 발사한다.</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonShockWave</t>
   </si>
   <si>
     <t>Warrior_NarrowSlash</t>
@@ -676,51 +715,15 @@
     <t>Prefabs/VFX/Warrior/MultiSlash</t>
   </si>
   <si>
-    <t>ProjectilePierce</t>
-  </si>
-  <si>
-    <t>Dragon_GodCall</t>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Dragon/DragonGodCall</t>
-  </si>
-  <si>
-    <t>Roar</t>
-  </si>
-  <si>
-    <t>투사체 관통 여부</t>
+    <t>중심에서 폭발</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>투사체일 경우 true면 대상/지형 충돌로 소멸하지 않고 최대사거리까지 이동</t>
+    <t>Dragon_Roar</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/VFX/Dragon/DragonBullet</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dragon_ShockWave</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dragon_Bullet</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>전방으로 5개의 관통 투사체를 발사한다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>전방으로 1개의 관통 투사체를 발사한다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Dragon/DragonShockWave</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주변 무작위 영역 10곳을 각각 1회 타격한다.</t>
+    <t>Prefabs/VFX/Dragon/DragonRoar</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -776,7 +779,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,6 +801,12 @@
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -863,7 +872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -934,6 +943,55 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1166,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1354,141 +1412,141 @@
         <v>30</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>222</v>
+        <v>31</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AQ2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AV2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AW2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AX2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AZ2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:52" s="7" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD3" s="6"/>
       <c r="AE3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF3" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
       <c r="AJ3" s="16" t="s">
-        <v>223</v>
+        <v>69</v>
       </c>
       <c r="AK3" s="6"/>
       <c r="AL3" s="6"/>
@@ -1500,338 +1558,338 @@
       <c r="AR3" s="6"/>
       <c r="AS3" s="6"/>
       <c r="AT3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
       <c r="AW3" s="6"/>
       <c r="AX3" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AY3" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AZ3" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="S4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="T4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="U4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="V4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="W4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="X4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="Y4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="Z4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z4" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="AA4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AL4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AM4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AN4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AP4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AQ4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AR4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AT4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AU4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AX4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AY4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AZ4" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="R5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="V5" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="W5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="Y5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AE5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="AA5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD5" s="8" t="s">
+      <c r="AF5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AE5" s="8" t="s">
+      <c r="AR5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AF5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG5" s="8" t="s">
+      <c r="AT5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AH5" s="8" t="s">
+      <c r="AU5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AI5" s="8" t="s">
+      <c r="AV5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AJ5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK5" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AQ5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AR5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AS5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AT5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AU5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AV5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW5" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="AX5" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AY5" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AZ5" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1848,20 +1906,20 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -1870,20 +1928,20 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AF6" s="8"/>
       <c r="AG6" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI6" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
@@ -1905,7 +1963,7 @@
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2019,160 +2077,160 @@
     </row>
     <row r="8" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AT8" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AU8" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AV8" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AW8" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AY8" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AZ8" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.3">
@@ -2181,37 +2239,37 @@
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D9"/>
       <c r="E9" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F9"/>
       <c r="G9" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H9"/>
       <c r="I9" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K9"/>
       <c r="L9" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M9"/>
       <c r="N9" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O9"/>
       <c r="P9" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R9" s="15" t="b">
         <v>1</v>
@@ -2223,7 +2281,7 @@
       <c r="U9"/>
       <c r="V9"/>
       <c r="W9"/>
-      <c r="X9"/>
+      <c r="X9" s="19"/>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
@@ -2240,19 +2298,19 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF9">
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AI9"/>
       <c r="AJ9" s="19"/>
@@ -2289,14 +2347,14 @@
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -2306,10 +2364,10 @@
       <c r="N10"/>
       <c r="O10"/>
       <c r="P10" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R10" s="15" t="b">
         <v>0</v>
@@ -2319,8 +2377,8 @@
       <c r="U10"/>
       <c r="V10"/>
       <c r="W10"/>
-      <c r="X10"/>
-      <c r="Y10"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
       <c r="Z10"/>
       <c r="AA10"/>
       <c r="AB10"/>
@@ -2333,13 +2391,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ10" s="19"/>
       <c r="AK10" s="3">
@@ -2363,117 +2421,117 @@
       <c r="AY10"/>
       <c r="AZ10"/>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A11"/>
-      <c r="B11" s="3">
+    <row r="11" spans="1:52" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
+      <c r="B11" s="24">
         <v>1003</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="L11" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="N11" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="O11" s="24">
+        <v>300</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q11" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="R11" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="24">
+        <v>5000</v>
+      </c>
+      <c r="Z11" s="24">
+        <v>30</v>
+      </c>
+      <c r="AA11" s="24">
+        <v>300</v>
+      </c>
+      <c r="AB11" s="24">
+        <v>1000</v>
+      </c>
+      <c r="AC11" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE11" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF11" s="24">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="D11"/>
-      <c r="E11" s="3" t="s">
+      <c r="AH11" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K11"/>
-      <c r="L11" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="M11"/>
-      <c r="N11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="O11" s="3">
-        <v>300</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>151</v>
-      </c>
-      <c r="R11" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="X11"/>
-      <c r="Y11" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>30</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB11" s="3">
+      <c r="AI11" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ11" s="27"/>
+      <c r="AK11" s="24">
+        <v>15</v>
+      </c>
+      <c r="AL11" s="23"/>
+      <c r="AM11" s="24">
+        <v>10</v>
+      </c>
+      <c r="AN11" s="24">
+        <v>10</v>
+      </c>
+      <c r="AO11" s="23"/>
+      <c r="AP11" s="23"/>
+      <c r="AQ11" s="23"/>
+      <c r="AR11" s="23"/>
+      <c r="AS11" s="24">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="24">
         <v>1000</v>
       </c>
-      <c r="AC11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="3">
-        <v>15</v>
-      </c>
-      <c r="AL11"/>
-      <c r="AM11" s="3">
-        <v>10</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>10</v>
-      </c>
-      <c r="AO11"/>
-      <c r="AP11"/>
-      <c r="AQ11"/>
-      <c r="AR11"/>
-      <c r="AS11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AU11" s="3">
+      <c r="AU11" s="24">
         <v>2000</v>
       </c>
-      <c r="AV11"/>
-      <c r="AW11"/>
-      <c r="AX11"/>
-      <c r="AY11"/>
-      <c r="AZ11"/>
+      <c r="AV11" s="23"/>
+      <c r="AW11" s="23"/>
+      <c r="AX11" s="23"/>
+      <c r="AY11" s="23"/>
+      <c r="AZ11" s="23"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A12"/>
@@ -2481,37 +2539,37 @@
         <v>1008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R12" s="15" t="b">
         <v>0</v>
@@ -2521,7 +2579,7 @@
       <c r="U12"/>
       <c r="V12"/>
       <c r="W12"/>
-      <c r="X12"/>
+      <c r="X12" s="19"/>
       <c r="Y12" s="3">
         <v>10000</v>
       </c>
@@ -2538,22 +2596,22 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
       </c>
       <c r="AG12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AJ12" s="19"/>
       <c r="AK12" s="3">
@@ -2587,26 +2645,26 @@
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B13" s="3">
         <v>1004</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D13"/>
       <c r="E13" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K13"/>
       <c r="L13"/>
@@ -2614,10 +2672,10 @@
       <c r="N13"/>
       <c r="O13"/>
       <c r="P13" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R13" s="15" t="b">
         <v>0</v>
@@ -2627,13 +2685,13 @@
         <v>1005</v>
       </c>
       <c r="U13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="V13"/>
       <c r="W13" t="s">
-        <v>178</v>
-      </c>
-      <c r="X13"/>
+        <v>181</v>
+      </c>
+      <c r="X13" s="19"/>
       <c r="Y13" s="3">
         <v>600</v>
       </c>
@@ -2651,7 +2709,7 @@
       </c>
       <c r="AD13"/>
       <c r="AE13" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF13" s="3">
         <v>0</v>
@@ -2685,13 +2743,13 @@
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B14" s="3">
         <v>1005</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -2706,10 +2764,10 @@
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R14" s="15" t="b">
         <v>0</v>
@@ -2719,8 +2777,8 @@
       <c r="U14"/>
       <c r="V14"/>
       <c r="W14"/>
-      <c r="X14"/>
-      <c r="Y14"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
       <c r="Z14"/>
       <c r="AA14"/>
       <c r="AB14"/>
@@ -2733,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="AG14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ14" s="19"/>
       <c r="AK14" s="3">
@@ -2765,26 +2823,26 @@
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B15" s="3">
         <v>1006</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D15"/>
       <c r="E15" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K15"/>
       <c r="L15"/>
@@ -2792,10 +2850,10 @@
       <c r="N15"/>
       <c r="O15"/>
       <c r="P15" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R15" s="15" t="b">
         <v>0</v>
@@ -2805,13 +2863,13 @@
         <v>1007</v>
       </c>
       <c r="U15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>183</v>
-      </c>
-      <c r="X15"/>
+        <v>186</v>
+      </c>
+      <c r="X15" s="19"/>
       <c r="Y15" s="3">
         <v>20000</v>
       </c>
@@ -2828,22 +2886,22 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF15">
         <v>25</v>
       </c>
       <c r="AG15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AJ15" s="19"/>
       <c r="AK15" s="3">
@@ -2879,13 +2937,13 @@
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" s="3">
         <v>1007</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -2900,10 +2958,10 @@
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R16" s="15" t="b">
         <v>0</v>
@@ -2913,8 +2971,8 @@
       <c r="U16"/>
       <c r="V16"/>
       <c r="W16"/>
-      <c r="X16"/>
-      <c r="Y16"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
       <c r="Z16"/>
       <c r="AA16"/>
       <c r="AB16"/>
@@ -2927,13 +2985,13 @@
         <v>0</v>
       </c>
       <c r="AG16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AJ16" s="19"/>
       <c r="AK16" s="3">
@@ -2969,26 +3027,26 @@
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B17" s="3">
         <v>1012</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D17"/>
       <c r="E17" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
@@ -2996,10 +3054,10 @@
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R17" s="15" t="b">
         <v>0</v>
@@ -3009,7 +3067,7 @@
       <c r="U17"/>
       <c r="V17"/>
       <c r="W17"/>
-      <c r="X17"/>
+      <c r="X17" s="19"/>
       <c r="Y17" s="3">
         <v>10000</v>
       </c>
@@ -3021,19 +3079,19 @@
       </c>
       <c r="AD17"/>
       <c r="AE17" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF17" s="3">
         <v>0</v>
       </c>
       <c r="AG17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ17" s="19"/>
       <c r="AK17" s="3">
@@ -3063,26 +3121,26 @@
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B18" s="3">
         <v>1009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D18"/>
       <c r="E18" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
@@ -3090,10 +3148,10 @@
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q18" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R18" s="15" t="b">
         <v>0</v>
@@ -3103,7 +3161,7 @@
       <c r="U18"/>
       <c r="V18"/>
       <c r="W18"/>
-      <c r="X18"/>
+      <c r="X18" s="19"/>
       <c r="Y18" s="3">
         <v>300</v>
       </c>
@@ -3121,7 +3179,7 @@
       </c>
       <c r="AD18"/>
       <c r="AE18" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF18" s="3">
         <v>0</v>
@@ -3153,45 +3211,45 @@
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B19" s="3">
         <v>1010</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D19"/>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G19"/>
       <c r="H19" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O19"/>
       <c r="P19" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R19" s="15" t="b">
         <v>0</v>
@@ -3201,13 +3259,13 @@
         <v>1011</v>
       </c>
       <c r="U19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="V19"/>
       <c r="W19" t="s">
-        <v>183</v>
-      </c>
-      <c r="X19"/>
+        <v>186</v>
+      </c>
+      <c r="X19" s="19"/>
       <c r="Y19" s="3">
         <v>20000</v>
       </c>
@@ -3224,22 +3282,22 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AE19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ19" s="19"/>
       <c r="AK19" s="3">
@@ -3269,13 +3327,13 @@
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B20" s="3">
         <v>1011</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -3290,10 +3348,10 @@
       <c r="N20"/>
       <c r="O20"/>
       <c r="P20" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R20" s="15" t="b">
         <v>0</v>
@@ -3303,8 +3361,8 @@
       <c r="U20"/>
       <c r="V20"/>
       <c r="W20"/>
-      <c r="X20"/>
-      <c r="Y20"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
       <c r="Z20"/>
       <c r="AA20"/>
       <c r="AB20"/>
@@ -3317,13 +3375,13 @@
         <v>0</v>
       </c>
       <c r="AG20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH20" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI20" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ20" s="19"/>
       <c r="AK20" s="3">
@@ -3363,10 +3421,10 @@
         <v>9001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -3381,7 +3439,7 @@
       <c r="O21"/>
       <c r="P21"/>
       <c r="Q21" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R21" s="15" t="b">
         <v>0</v>
@@ -3391,7 +3449,7 @@
       <c r="U21"/>
       <c r="V21"/>
       <c r="W21"/>
-      <c r="X21"/>
+      <c r="X21" s="19"/>
       <c r="Y21" s="3">
         <v>1500</v>
       </c>
@@ -3406,20 +3464,20 @@
         <v>1</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE21" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF21" s="3">
         <v>1.25</v>
       </c>
       <c r="AG21"/>
       <c r="AH21" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AK21" s="3">
         <v>5</v>
@@ -3452,15 +3510,15 @@
         <v>9002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -3472,7 +3530,7 @@
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R22"/>
       <c r="S22"/>
@@ -3480,7 +3538,7 @@
       <c r="U22"/>
       <c r="V22"/>
       <c r="W22"/>
-      <c r="X22"/>
+      <c r="X22" s="19"/>
       <c r="Y22" s="3">
         <v>4000</v>
       </c>
@@ -3495,20 +3553,20 @@
         <v>1</v>
       </c>
       <c r="AD22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE22" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
       <c r="AG22"/>
       <c r="AH22" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AK22" s="3">
         <v>8</v>
@@ -3541,19 +3599,19 @@
         <v>9101</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23" s="17" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="H23"/>
       <c r="I23" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J23"/>
       <c r="K23"/>
@@ -3563,7 +3621,7 @@
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R23"/>
       <c r="S23"/>
@@ -3571,7 +3629,7 @@
       <c r="U23"/>
       <c r="V23"/>
       <c r="W23"/>
-      <c r="X23"/>
+      <c r="X23" s="19"/>
       <c r="Y23" s="3">
         <v>2500</v>
       </c>
@@ -3586,22 +3644,22 @@
         <v>1</v>
       </c>
       <c r="AD23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE23" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF23" s="3">
         <v>0</v>
       </c>
       <c r="AG23" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH23" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ23" s="3" t="b">
         <v>1</v>
@@ -3650,20 +3708,20 @@
       <c r="B24" s="3">
         <v>9102</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>219</v>
+      <c r="C24" s="20" t="s">
+        <v>209</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24" t="s">
-        <v>220</v>
+      <c r="H24" s="17" t="s">
+        <v>211</v>
       </c>
       <c r="I24" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
@@ -3673,7 +3731,7 @@
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R24"/>
       <c r="S24"/>
@@ -3681,7 +3739,7 @@
       <c r="U24"/>
       <c r="V24"/>
       <c r="W24"/>
-      <c r="X24"/>
+      <c r="X24" s="19"/>
       <c r="Y24" s="3">
         <v>9000</v>
       </c>
@@ -3696,22 +3754,22 @@
         <v>1</v>
       </c>
       <c r="AD24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
       <c r="AG24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH24" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AK24" s="3">
         <v>22</v>
@@ -3764,19 +3822,19 @@
         <v>9103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="I25" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
@@ -3786,7 +3844,7 @@
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R25"/>
       <c r="S25"/>
@@ -3794,7 +3852,7 @@
       <c r="U25"/>
       <c r="V25"/>
       <c r="W25"/>
-      <c r="X25">
+      <c r="X25" s="19">
         <v>14</v>
       </c>
       <c r="Y25" s="3">
@@ -3811,22 +3869,22 @@
         <v>1</v>
       </c>
       <c r="AD25" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF25" s="3">
         <v>12</v>
       </c>
       <c r="AG25" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AH25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AK25" s="3">
         <v>8</v>
@@ -3865,19 +3923,19 @@
         <v>9104</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" s="17" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
@@ -3887,7 +3945,7 @@
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R26"/>
       <c r="S26"/>
@@ -3895,7 +3953,7 @@
       <c r="U26"/>
       <c r="V26"/>
       <c r="W26"/>
-      <c r="X26"/>
+      <c r="X26" s="19"/>
       <c r="Y26" s="3">
         <v>10000</v>
       </c>
@@ -3910,22 +3968,22 @@
         <v>1</v>
       </c>
       <c r="AD26" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
       <c r="AG26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH26" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AI26" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AJ26" s="3" t="b">
         <v>1</v>
@@ -3953,165 +4011,126 @@
       <c r="AS26"/>
       <c r="AT26"/>
       <c r="AU26"/>
-      <c r="AV26"/>
       <c r="AW26"/>
       <c r="AX26"/>
       <c r="AY26"/>
       <c r="AZ26"/>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A27"/>
-      <c r="B27" s="19">
-        <v>2001</v>
-      </c>
-      <c r="C27" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27" t="s">
-        <v>208</v>
-      </c>
-      <c r="I27" t="s">
-        <v>209</v>
-      </c>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="R27" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27"/>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27"/>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>600</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>400</v>
-      </c>
-      <c r="AB27">
-        <v>500</v>
-      </c>
-      <c r="AC27" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF27">
-        <v>5</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ27" s="19"/>
-      <c r="AK27">
-        <v>50</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>10</v>
-      </c>
-      <c r="AN27">
-        <v>10</v>
-      </c>
-      <c r="AO27">
-        <v>0</v>
-      </c>
-      <c r="AP27">
-        <v>8</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27">
-        <v>600</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
-      </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
-      <c r="AX27">
-        <v>0</v>
-      </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
+    <row r="27" spans="1:52" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="23"/>
+      <c r="B27" s="27">
+        <v>9105</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="H27" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="R27" s="30"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="31">
+        <v>10000</v>
+      </c>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31">
+        <v>1000</v>
+      </c>
+      <c r="AB27" s="31">
+        <v>1000</v>
+      </c>
+      <c r="AC27" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE27" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF27" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH27" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI27" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK27" s="31">
+        <v>100</v>
+      </c>
+      <c r="AL27" s="31">
+        <v>20</v>
+      </c>
+      <c r="AM27" s="31"/>
+      <c r="AN27" s="31"/>
+      <c r="AO27" s="31"/>
+      <c r="AP27" s="31"/>
+      <c r="AQ27" s="31"/>
+      <c r="AR27" s="31"/>
+      <c r="AS27" s="31">
+        <v>0</v>
+      </c>
+      <c r="AT27" s="31">
+        <v>1000</v>
+      </c>
+      <c r="AU27" s="31">
+        <v>2000</v>
+      </c>
+      <c r="AV27"/>
+      <c r="AW27" s="31"/>
+      <c r="AX27" s="31"/>
+      <c r="AY27" s="31"/>
+      <c r="AZ27" s="31"/>
     </row>
     <row r="28" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A28"/>
       <c r="B28" s="19">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D28" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I28" t="s">
-        <v>214</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
       <c r="M28"/>
@@ -4120,13 +4139,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R28" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -4139,112 +4158,113 @@
         <v>0</v>
       </c>
       <c r="W28"/>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>2500</v>
-      </c>
-      <c r="Z28">
+      <c r="X28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="21">
+        <v>600</v>
+      </c>
+      <c r="Z28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="21">
+        <v>400</v>
+      </c>
+      <c r="AB28" s="21">
+        <v>500</v>
+      </c>
+      <c r="AC28" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE28" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF28" s="21">
+        <v>5</v>
+      </c>
+      <c r="AG28" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH28" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI28" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ28" s="21"/>
+      <c r="AK28" s="21">
+        <v>50</v>
+      </c>
+      <c r="AL28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="21">
         <v>10</v>
       </c>
-      <c r="AA28">
-        <v>1200</v>
-      </c>
-      <c r="AB28">
-        <v>1500</v>
-      </c>
-      <c r="AC28" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF28">
-        <v>6</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ28" s="19"/>
-      <c r="AK28">
-        <v>100</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>18</v>
-      </c>
-      <c r="AN28">
-        <v>12</v>
-      </c>
-      <c r="AO28">
-        <v>0</v>
-      </c>
-      <c r="AP28">
-        <v>12</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>1000</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
+      <c r="AN28" s="21">
+        <v>10</v>
+      </c>
+      <c r="AO28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="21">
+        <v>8</v>
+      </c>
+      <c r="AQ28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="21">
+        <v>600</v>
+      </c>
+      <c r="AV28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AX28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AY28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A29"/>
       <c r="B29" s="19">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D29" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I29" t="s">
-        <v>209</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="J29"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29"/>
@@ -4253,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R29" s="18" t="b">
         <v>0</v>
@@ -4272,87 +4292,221 @@
         <v>0</v>
       </c>
       <c r="W29"/>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
+      <c r="X29" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="21">
+        <v>2500</v>
+      </c>
+      <c r="Z29" s="21">
+        <v>10</v>
+      </c>
+      <c r="AA29" s="21">
+        <v>1200</v>
+      </c>
+      <c r="AB29" s="21">
+        <v>1500</v>
+      </c>
+      <c r="AC29" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE29" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF29" s="21">
+        <v>6</v>
+      </c>
+      <c r="AG29" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH29" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI29" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ29" s="21"/>
+      <c r="AK29" s="21">
+        <v>100</v>
+      </c>
+      <c r="AL29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="21">
+        <v>18</v>
+      </c>
+      <c r="AN29" s="21">
+        <v>12</v>
+      </c>
+      <c r="AO29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="21">
+        <v>12</v>
+      </c>
+      <c r="AQ29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="21">
+        <v>1000</v>
+      </c>
+      <c r="AV29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AX29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AY29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AZ29" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="A30"/>
+      <c r="B30">
+        <v>2003</v>
+      </c>
+      <c r="C30" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30" t="s">
+        <v>230</v>
+      </c>
+      <c r="I30" t="s">
+        <v>222</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>154</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30"/>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30"/>
+      <c r="X30" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="21">
         <v>4000</v>
       </c>
-      <c r="Z29">
+      <c r="Z30" s="21">
         <v>15</v>
       </c>
-      <c r="AA29">
+      <c r="AA30" s="21">
         <v>400</v>
       </c>
-      <c r="AB29">
+      <c r="AB30" s="21">
         <v>1000</v>
       </c>
-      <c r="AC29" s="18" t="b">
+      <c r="AC30" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="AD29"/>
-      <c r="AE29" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ29" s="19"/>
-      <c r="AK29">
+      <c r="AD30" s="21"/>
+      <c r="AE30" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH30" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI30" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ30" s="21"/>
+      <c r="AK30" s="21">
         <v>30</v>
       </c>
-      <c r="AL29">
+      <c r="AL30" s="21">
         <v>5</v>
       </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>0</v>
-      </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
-      <c r="AP29">
+      <c r="AM30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="21">
         <v>5</v>
       </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
+      <c r="AQ30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT30" s="21">
         <v>250</v>
       </c>
-      <c r="AU29">
+      <c r="AU30" s="21">
         <v>1000</v>
       </c>
-      <c r="AV29">
-        <v>0</v>
-      </c>
-      <c r="AW29">
-        <v>0</v>
-      </c>
-      <c r="AX29">
-        <v>0</v>
-      </c>
-      <c r="AY29">
-        <v>0</v>
-      </c>
-      <c r="AZ29">
+      <c r="AV30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="21">
         <v>0</v>
       </c>
     </row>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC838415-4E73-4AB6-ADB1-E7BEE75D50B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2842E830-BF83-46E8-A54B-AD64B5227CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4087,7 +4087,7 @@
         <v>100</v>
       </c>
       <c r="AL27" s="31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AM27" s="31"/>
       <c r="AN27" s="31"/>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2842E830-BF83-46E8-A54B-AD64B5227CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C0BA2-6F5B-4D88-9FE1-9CDB62C0CAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="235">
   <si>
     <t>데이터이름</t>
   </si>
@@ -550,6 +550,9 @@
     <t>Sounds/Ultimate Magic Spells/Spell SFX/Loop -  Blue Energy Burn</t>
   </si>
   <si>
+    <t>Fireball_less</t>
+  </si>
+  <si>
     <t>//</t>
   </si>
   <si>
@@ -679,6 +682,15 @@
     <t>Prefabs/VFX/Dragon/DragonShockWave</t>
   </si>
   <si>
+    <t>Dragon_Roar</t>
+  </si>
+  <si>
+    <t>중심에서 폭발</t>
+  </si>
+  <si>
+    <t>Prefabs/VFX/Dragon/DragonRoar</t>
+  </si>
+  <si>
     <t>Warrior_NarrowSlash</t>
   </si>
   <si>
@@ -713,18 +725,6 @@
   </si>
   <si>
     <t>Prefabs/VFX/Warrior/MultiSlash</t>
-  </si>
-  <si>
-    <t>중심에서 폭발</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dragon_Roar</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/VFX/Dragon/DragonRoar</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -868,11 +868,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -911,33 +911,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -947,27 +924,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -975,27 +936,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="60% - 강조색1" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="60% - 강조색1" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="메모" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1010,23 +956,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1224,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1236,21 +1165,31 @@
     <col min="7" max="7" width="63.125" style="3" customWidth="1"/>
     <col min="8" max="8" width="73.75" style="3" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="3" customWidth="1"/>
-    <col min="10" max="14" width="21.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.125" customWidth="1"/>
+    <col min="11" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="13" style="3" customWidth="1"/>
     <col min="15" max="15" width="24.125" style="3" customWidth="1"/>
     <col min="16" max="16" width="19.25" style="3" customWidth="1"/>
     <col min="17" max="17" width="17.5" style="3" customWidth="1"/>
-    <col min="18" max="19" width="19.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.125" customWidth="1"/>
+    <col min="19" max="19" width="13" style="3" customWidth="1"/>
     <col min="20" max="20" width="18.25" style="3" customWidth="1"/>
     <col min="21" max="21" width="23" style="3" customWidth="1"/>
     <col min="22" max="22" width="23.125" style="3" customWidth="1"/>
-    <col min="23" max="24" width="18.25" style="3" customWidth="1"/>
+    <col min="23" max="23" width="18.25" customWidth="1"/>
+    <col min="24" max="24" width="13" style="3" customWidth="1"/>
     <col min="25" max="25" width="20.875" style="3" customWidth="1"/>
-    <col min="26" max="31" width="18.25" style="3" customWidth="1"/>
+    <col min="26" max="26" width="18.25" customWidth="1"/>
+    <col min="27" max="30" width="13" customWidth="1"/>
+    <col min="31" max="31" width="13" style="3" customWidth="1"/>
     <col min="32" max="32" width="24" style="3" customWidth="1"/>
-    <col min="33" max="39" width="18.25" style="3" customWidth="1"/>
+    <col min="33" max="33" width="18.25" customWidth="1"/>
+    <col min="34" max="38" width="13" customWidth="1"/>
+    <col min="39" max="39" width="13" style="3" customWidth="1"/>
     <col min="40" max="40" width="20.75" style="3" customWidth="1"/>
-    <col min="41" max="52" width="18.25" style="3" customWidth="1"/>
+    <col min="41" max="41" width="18.25" customWidth="1"/>
+    <col min="42" max="51" width="13" customWidth="1"/>
+    <col min="52" max="52" width="13" style="3" customWidth="1"/>
     <col min="53" max="53" width="9" style="3" customWidth="1"/>
     <col min="54" max="16384" width="9" style="3"/>
   </cols>
@@ -1276,42 +1215,6 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1"/>
-      <c r="R1"/>
-      <c r="S1"/>
-      <c r="T1"/>
-      <c r="U1"/>
-      <c r="V1"/>
-      <c r="W1"/>
-      <c r="X1"/>
-      <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-      <c r="AB1"/>
-      <c r="AC1"/>
-      <c r="AD1"/>
-      <c r="AE1"/>
-      <c r="AF1"/>
-      <c r="AG1"/>
-      <c r="AH1"/>
-      <c r="AI1"/>
-      <c r="AJ1"/>
-      <c r="AK1"/>
-      <c r="AL1"/>
-      <c r="AM1"/>
-      <c r="AN1"/>
-      <c r="AO1"/>
-      <c r="AP1"/>
-      <c r="AQ1"/>
-      <c r="AR1"/>
-      <c r="AS1"/>
-      <c r="AT1"/>
-      <c r="AU1"/>
-      <c r="AV1"/>
-      <c r="AW1"/>
-      <c r="AX1"/>
-      <c r="AY1"/>
-      <c r="AZ1"/>
     </row>
     <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1539,13 +1442,13 @@
       <c r="AE3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="AF3" s="16" t="s">
+      <c r="AF3" s="14" t="s">
         <v>68</v>
       </c>
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
-      <c r="AJ3" s="16" t="s">
+      <c r="AJ3" s="14" t="s">
         <v>69</v>
       </c>
       <c r="AK3" s="6"/>
@@ -1983,7 +1886,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="14" t="b">
+      <c r="R7" s="8" t="b">
         <v>0</v>
       </c>
       <c r="S7" s="8">
@@ -2012,7 +1915,7 @@
       <c r="AB7" s="8">
         <v>0</v>
       </c>
-      <c r="AC7" s="14" t="b">
+      <c r="AC7" s="8" t="b">
         <v>1</v>
       </c>
       <c r="AD7" s="8"/>
@@ -2234,54 +2137,43 @@
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A9"/>
       <c r="B9" s="3">
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D9"/>
       <c r="E9" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F9"/>
       <c r="G9" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H9"/>
       <c r="I9" s="13" t="s">
         <v>149</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K9"/>
       <c r="L9" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="M9"/>
       <c r="N9" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="O9"/>
       <c r="P9" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q9" t="s">
         <v>154</v>
       </c>
-      <c r="R9" s="15" t="b">
+      <c r="R9" s="3" t="b">
         <v>1</v>
       </c>
       <c r="S9" s="3">
         <v>1002</v>
       </c>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9" s="19"/>
+      <c r="X9" s="16"/>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
@@ -2294,7 +2186,7 @@
       <c r="AB9" s="3">
         <v>300</v>
       </c>
-      <c r="AC9" s="15" t="b">
+      <c r="AC9" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD9" t="s">
@@ -2312,19 +2204,15 @@
       <c r="AH9" t="s">
         <v>158</v>
       </c>
-      <c r="AI9"/>
-      <c r="AJ9" s="19"/>
+      <c r="AJ9" s="16"/>
       <c r="AK9" s="3">
         <v>50</v>
       </c>
-      <c r="AL9"/>
-      <c r="AM9"/>
-      <c r="AN9"/>
       <c r="AO9" s="3">
         <v>15</v>
       </c>
       <c r="AP9" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AQ9" s="3">
         <v>5</v>
@@ -2332,61 +2220,31 @@
       <c r="AR9" s="3">
         <v>90</v>
       </c>
-      <c r="AS9"/>
-      <c r="AT9"/>
-      <c r="AU9"/>
-      <c r="AV9"/>
-      <c r="AW9"/>
-      <c r="AX9"/>
-      <c r="AY9"/>
-      <c r="AZ9"/>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A10"/>
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
       <c r="H10" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
       <c r="P10" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q10" t="s">
         <v>154</v>
       </c>
-      <c r="R10" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10"/>
-      <c r="AA10"/>
-      <c r="AB10"/>
-      <c r="AC10" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD10"/>
-      <c r="AE10"/>
+      <c r="R10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="AC10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="AF10">
         <v>0</v>
       </c>
@@ -2399,142 +2257,127 @@
       <c r="AI10" t="s">
         <v>163</v>
       </c>
-      <c r="AJ10" s="19"/>
+      <c r="AJ10" s="16"/>
       <c r="AK10" s="3">
         <v>30</v>
       </c>
       <c r="AL10" s="3">
         <v>5</v>
       </c>
-      <c r="AM10"/>
-      <c r="AN10"/>
-      <c r="AO10"/>
-      <c r="AP10"/>
-      <c r="AQ10"/>
-      <c r="AR10"/>
-      <c r="AS10"/>
-      <c r="AT10"/>
-      <c r="AU10"/>
-      <c r="AV10"/>
-      <c r="AW10"/>
-      <c r="AX10"/>
-      <c r="AY10"/>
-      <c r="AZ10"/>
     </row>
-    <row r="11" spans="1:52" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+    <row r="11" spans="1:52" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20">
         <v>1003</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="s">
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24" t="s">
+      <c r="K11" s="19"/>
+      <c r="L11" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="24" t="s">
+      <c r="M11" s="19"/>
+      <c r="N11" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="20">
         <v>300</v>
       </c>
-      <c r="P11" s="24" t="s">
+      <c r="P11" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="Q11" s="23" t="s">
+      <c r="Q11" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="R11" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="24">
+      <c r="R11" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="20">
         <v>5000</v>
       </c>
-      <c r="Z11" s="24">
+      <c r="Z11" s="20">
         <v>30</v>
       </c>
-      <c r="AA11" s="24">
+      <c r="AA11" s="20">
         <v>300</v>
       </c>
-      <c r="AB11" s="24">
+      <c r="AB11" s="20">
         <v>1000</v>
       </c>
-      <c r="AC11" s="26" t="b">
+      <c r="AC11" s="20" t="b">
         <v>1</v>
       </c>
-      <c r="AD11" s="23" t="s">
+      <c r="AD11" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="AE11" s="24" t="s">
+      <c r="AE11" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="AF11" s="24">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="23" t="s">
+      <c r="AF11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="AH11" s="23" t="s">
+      <c r="AH11" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="AI11" s="23" t="s">
+      <c r="AI11" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="24">
+      <c r="AJ11" s="22"/>
+      <c r="AK11" s="20">
         <v>15</v>
       </c>
-      <c r="AL11" s="23"/>
-      <c r="AM11" s="24">
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="20">
         <v>10</v>
       </c>
-      <c r="AN11" s="24">
+      <c r="AN11" s="20">
         <v>10</v>
       </c>
-      <c r="AO11" s="23"/>
-      <c r="AP11" s="23"/>
-      <c r="AQ11" s="23"/>
-      <c r="AR11" s="23"/>
-      <c r="AS11" s="24">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="24">
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="20">
         <v>1000</v>
       </c>
-      <c r="AU11" s="24">
+      <c r="AU11" s="20">
         <v>2000</v>
       </c>
-      <c r="AV11" s="23"/>
-      <c r="AW11" s="23"/>
-      <c r="AX11" s="23"/>
-      <c r="AY11" s="23"/>
-      <c r="AZ11" s="23"/>
+      <c r="AV11" s="19"/>
+      <c r="AW11" s="19"/>
+      <c r="AX11" s="19"/>
+      <c r="AY11" s="19"/>
+      <c r="AZ11" s="19"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A12"/>
       <c r="B12" s="3">
         <v>1008</v>
       </c>
@@ -2547,8 +2390,6 @@
       <c r="E12" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F12"/>
-      <c r="G12"/>
       <c r="H12" s="3" t="s">
         <v>174</v>
       </c>
@@ -2558,28 +2399,19 @@
       <c r="J12" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K12"/>
-      <c r="L12"/>
       <c r="M12" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="N12"/>
-      <c r="O12"/>
       <c r="P12" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q12" t="s">
         <v>154</v>
       </c>
-      <c r="R12" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12" s="19"/>
+      <c r="R12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" s="16"/>
       <c r="Y12" s="3">
         <v>10000</v>
       </c>
@@ -2592,7 +2424,7 @@
       <c r="AB12" s="3">
         <v>500</v>
       </c>
-      <c r="AC12" s="15" t="b">
+      <c r="AC12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD12" t="s">
@@ -2613,21 +2445,16 @@
       <c r="AI12" t="s">
         <v>170</v>
       </c>
-      <c r="AJ12" s="19"/>
+      <c r="AJ12" s="16"/>
       <c r="AK12" s="3">
         <v>40</v>
       </c>
-      <c r="AL12"/>
       <c r="AM12" s="3">
         <v>20</v>
       </c>
       <c r="AN12" s="3">
         <v>20</v>
       </c>
-      <c r="AO12"/>
-      <c r="AP12"/>
-      <c r="AQ12"/>
-      <c r="AR12"/>
       <c r="AS12" s="3">
         <v>0</v>
       </c>
@@ -2637,262 +2464,185 @@
       <c r="AU12" s="3">
         <v>5000</v>
       </c>
-      <c r="AV12"/>
-      <c r="AW12"/>
-      <c r="AX12"/>
-      <c r="AY12"/>
-      <c r="AZ12"/>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="B13" s="3">
+        <v>1014</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="3">
-        <v>1004</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
+      <c r="G13" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="I13" s="13" t="s">
         <v>149</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
+      <c r="L13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="P13" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q13" t="s">
-        <v>179</v>
-      </c>
-      <c r="R13" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13"/>
-      <c r="T13" s="3">
-        <v>1005</v>
-      </c>
-      <c r="U13" t="s">
-        <v>180</v>
-      </c>
-      <c r="V13"/>
-      <c r="W13" t="s">
-        <v>181</v>
-      </c>
-      <c r="X13" s="19"/>
+        <v>154</v>
+      </c>
+      <c r="R13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1002</v>
+      </c>
+      <c r="X13" s="16"/>
       <c r="Y13" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="3">
+        <v>50</v>
+      </c>
+      <c r="AO13" s="3">
         <v>15</v>
       </c>
-      <c r="AA13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD13"/>
-      <c r="AE13" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG13"/>
-      <c r="AH13"/>
-      <c r="AI13"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL13"/>
-      <c r="AM13"/>
-      <c r="AN13"/>
-      <c r="AO13"/>
-      <c r="AP13"/>
-      <c r="AQ13"/>
-      <c r="AR13"/>
-      <c r="AS13"/>
-      <c r="AT13"/>
-      <c r="AU13"/>
-      <c r="AV13" s="3">
-        <v>10</v>
-      </c>
-      <c r="AW13" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AX13"/>
-      <c r="AY13"/>
-      <c r="AZ13"/>
+      <c r="AP13" s="3">
+        <v>30</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>3</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>176</v>
+      <c r="A14" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B14" s="3">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
+        <v>178</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="P14" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q14" t="s">
-        <v>154</v>
-      </c>
-      <c r="R14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14"/>
-      <c r="T14"/>
-      <c r="U14"/>
-      <c r="V14"/>
-      <c r="W14"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14"/>
-      <c r="AA14"/>
-      <c r="AB14"/>
-      <c r="AC14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14"/>
-      <c r="AE14"/>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ14" s="19"/>
+        <v>180</v>
+      </c>
+      <c r="R14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1005</v>
+      </c>
+      <c r="U14" t="s">
+        <v>181</v>
+      </c>
+      <c r="W14" t="s">
+        <v>182</v>
+      </c>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>15</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="16"/>
       <c r="AK14" s="3">
-        <v>20</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM14"/>
-      <c r="AN14"/>
-      <c r="AO14"/>
-      <c r="AP14"/>
-      <c r="AQ14"/>
-      <c r="AR14"/>
-      <c r="AS14"/>
-      <c r="AT14"/>
-      <c r="AU14"/>
-      <c r="AV14"/>
-      <c r="AW14"/>
-      <c r="AX14"/>
-      <c r="AY14"/>
-      <c r="AZ14"/>
+        <v>0</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>10</v>
+      </c>
+      <c r="AW14" s="3">
+        <v>1000</v>
+      </c>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>176</v>
+      <c r="A15" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B15" s="3">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D15"/>
-      <c r="E15" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
       <c r="P15" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q15" t="s">
         <v>154</v>
       </c>
-      <c r="R15" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15"/>
-      <c r="T15" s="3">
-        <v>1007</v>
-      </c>
-      <c r="U15" t="s">
-        <v>180</v>
-      </c>
-      <c r="V15"/>
-      <c r="W15" t="s">
-        <v>186</v>
-      </c>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>80</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AC15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>182</v>
+      <c r="R15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="AC15" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="s">
         <v>161</v>
@@ -2901,88 +2651,77 @@
         <v>162</v>
       </c>
       <c r="AI15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ15" s="19"/>
+        <v>163</v>
+      </c>
+      <c r="AJ15" s="16"/>
       <c r="AK15" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AL15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>50</v>
-      </c>
-      <c r="AO15"/>
-      <c r="AP15"/>
-      <c r="AQ15"/>
-      <c r="AR15"/>
-      <c r="AS15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="3">
-        <v>300</v>
-      </c>
-      <c r="AU15" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AV15"/>
-      <c r="AW15"/>
-      <c r="AX15"/>
-      <c r="AY15"/>
-      <c r="AZ15"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>176</v>
+      <c r="A16" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B16" s="3">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
+        <v>185</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="P16" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q16" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16"/>
-      <c r="AA16"/>
-      <c r="AB16"/>
-      <c r="AC16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD16"/>
-      <c r="AE16"/>
+      <c r="R16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3">
+        <v>1007</v>
+      </c>
+      <c r="U16" t="s">
+        <v>181</v>
+      </c>
+      <c r="W16" t="s">
+        <v>187</v>
+      </c>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>183</v>
+      </c>
       <c r="AF16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="s">
         <v>161</v>
@@ -2993,9 +2732,9 @@
       <c r="AI16" t="s">
         <v>170</v>
       </c>
-      <c r="AJ16" s="19"/>
+      <c r="AJ16" s="16"/>
       <c r="AK16" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AL16" s="3">
         <v>5</v>
@@ -3006,82 +2745,41 @@
       <c r="AN16" s="3">
         <v>50</v>
       </c>
-      <c r="AO16"/>
-      <c r="AP16"/>
-      <c r="AQ16"/>
-      <c r="AR16"/>
       <c r="AS16" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AT16" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AU16" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AV16"/>
-      <c r="AW16"/>
-      <c r="AX16"/>
-      <c r="AY16"/>
-      <c r="AZ16"/>
+        <v>3000</v>
+      </c>
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>176</v>
+      <c r="A17" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B17" s="3">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D17"/>
-      <c r="E17" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
       <c r="P17" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q17" t="s">
         <v>154</v>
       </c>
-      <c r="R17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17"/>
-      <c r="T17"/>
-      <c r="U17"/>
-      <c r="V17"/>
-      <c r="W17"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Z17"/>
-      <c r="AA17"/>
-      <c r="AB17"/>
-      <c r="AC17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD17"/>
-      <c r="AE17" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="R17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="AC17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>0</v>
       </c>
       <c r="AG17" t="s">
@@ -3091,144 +2789,107 @@
         <v>162</v>
       </c>
       <c r="AI17" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ17" s="19"/>
+        <v>170</v>
+      </c>
+      <c r="AJ17" s="16"/>
       <c r="AK17" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AL17" s="3">
-        <v>10</v>
-      </c>
-      <c r="AM17"/>
-      <c r="AN17"/>
-      <c r="AO17"/>
-      <c r="AP17"/>
-      <c r="AQ17"/>
-      <c r="AR17"/>
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
+        <v>50</v>
+      </c>
       <c r="AS17" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AT17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU17"/>
-      <c r="AV17"/>
-      <c r="AW17"/>
-      <c r="AX17"/>
-      <c r="AY17"/>
-      <c r="AZ17"/>
+        <v>1000</v>
+      </c>
+      <c r="AU17" s="3">
+        <v>5000</v>
+      </c>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>176</v>
+      <c r="A18" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B18" s="3">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D18"/>
-      <c r="E18" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
       <c r="I18" s="13" t="s">
         <v>149</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
       <c r="P18" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q18" t="s">
-        <v>179</v>
-      </c>
-      <c r="R18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18"/>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="W18"/>
-      <c r="X18" s="19"/>
+        <v>154</v>
+      </c>
+      <c r="R18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="16"/>
       <c r="Y18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AC18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ18" s="16"/>
+      <c r="AK18" s="3">
+        <v>30</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>10</v>
+      </c>
+      <c r="AS18" s="3">
         <v>300</v>
       </c>
-      <c r="Z18" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC18" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD18"/>
-      <c r="AE18" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG18"/>
-      <c r="AH18"/>
-      <c r="AI18"/>
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL18"/>
-      <c r="AM18"/>
-      <c r="AN18"/>
-      <c r="AO18"/>
-      <c r="AP18"/>
-      <c r="AQ18"/>
-      <c r="AR18"/>
-      <c r="AS18"/>
-      <c r="AT18"/>
-      <c r="AU18"/>
-      <c r="AV18" s="3">
-        <v>5</v>
-      </c>
-      <c r="AW18"/>
-      <c r="AX18"/>
-      <c r="AY18"/>
-      <c r="AZ18"/>
+      <c r="AT18" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
-        <v>176</v>
+      <c r="A19" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B19" s="3">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="D19"/>
-      <c r="E19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G19"/>
-      <c r="H19" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>149</v>
@@ -3236,141 +2897,116 @@
       <c r="J19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="O19"/>
       <c r="P19" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q19" t="s">
-        <v>154</v>
-      </c>
-      <c r="R19" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19"/>
-      <c r="T19" s="3">
-        <v>1011</v>
-      </c>
-      <c r="U19" t="s">
         <v>180</v>
       </c>
-      <c r="V19"/>
-      <c r="W19" t="s">
-        <v>186</v>
-      </c>
-      <c r="X19" s="19"/>
+      <c r="R19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" s="16"/>
       <c r="Y19" s="3">
-        <v>20000</v>
+        <v>300</v>
       </c>
       <c r="Z19" s="3">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="AA19" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AC19" s="15" t="b">
+        <v>300</v>
+      </c>
+      <c r="AC19" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AD19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ19" s="19"/>
+      <c r="AE19" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="16"/>
       <c r="AK19" s="3">
-        <v>50</v>
-      </c>
-      <c r="AL19" s="3">
-        <v>10</v>
-      </c>
-      <c r="AM19"/>
-      <c r="AN19"/>
-      <c r="AO19"/>
-      <c r="AP19"/>
-      <c r="AQ19"/>
-      <c r="AR19"/>
-      <c r="AS19" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AT19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU19"/>
-      <c r="AV19"/>
-      <c r="AW19"/>
-      <c r="AX19"/>
-      <c r="AY19"/>
-      <c r="AZ19"/>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>176</v>
+      <c r="A20" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B20" s="3">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
-      <c r="O20"/>
+        <v>193</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="P20" s="3" t="s">
         <v>153</v>
       </c>
       <c r="Q20" t="s">
         <v>154</v>
       </c>
-      <c r="R20" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20"/>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20"/>
-      <c r="W20"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20"/>
-      <c r="AA20"/>
-      <c r="AB20"/>
-      <c r="AC20" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD20"/>
-      <c r="AE20"/>
+      <c r="R20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1011</v>
+      </c>
+      <c r="U20" t="s">
+        <v>181</v>
+      </c>
+      <c r="W20" t="s">
+        <v>187</v>
+      </c>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>73</v>
+      </c>
       <c r="AF20">
         <v>0</v>
       </c>
@@ -3383,264 +3019,163 @@
       <c r="AI20" t="s">
         <v>163</v>
       </c>
-      <c r="AJ20" s="19"/>
+      <c r="AJ20" s="16"/>
       <c r="AK20" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AL20" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM20"/>
-      <c r="AN20"/>
-      <c r="AO20"/>
-      <c r="AP20"/>
-      <c r="AQ20"/>
-      <c r="AR20"/>
+        <v>10</v>
+      </c>
       <c r="AS20" s="3">
         <v>1000</v>
       </c>
       <c r="AT20" s="3">
         <v>0</v>
       </c>
-      <c r="AU20"/>
-      <c r="AV20"/>
-      <c r="AW20"/>
-      <c r="AX20" s="3">
-        <v>10</v>
-      </c>
-      <c r="AY20" s="3">
-        <v>10</v>
-      </c>
-      <c r="AZ20" s="3">
-        <v>15</v>
-      </c>
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A21"/>
+      <c r="A21" s="15" t="s">
+        <v>177</v>
+      </c>
       <c r="B21" s="3">
-        <v>9001</v>
+        <v>1011</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21" s="3" t="s">
+      <c r="P21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q21" t="s">
         <v>154</v>
       </c>
-      <c r="R21" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21"/>
-      <c r="T21"/>
-      <c r="U21"/>
-      <c r="V21"/>
-      <c r="W21"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z21"/>
-      <c r="AA21" s="3">
-        <v>350</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>250</v>
-      </c>
-      <c r="AC21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="AG21"/>
-      <c r="AH21" s="3" t="s">
+      <c r="R21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="AC21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH21" t="s">
         <v>162</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AI21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ21" s="16"/>
       <c r="AK21" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL21"/>
-      <c r="AM21" s="3">
+        <v>20</v>
+      </c>
+      <c r="AL21" s="3">
         <v>2</v>
       </c>
-      <c r="AN21" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="AO21"/>
-      <c r="AP21" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ21"/>
-      <c r="AR21"/>
-      <c r="AS21"/>
-      <c r="AT21"/>
-      <c r="AU21"/>
-      <c r="AV21"/>
-      <c r="AW21"/>
-      <c r="AX21"/>
-      <c r="AY21"/>
-      <c r="AZ21"/>
+      <c r="AS21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AT21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AY21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AZ21" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A22"/>
       <c r="B22" s="3">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
-      <c r="P22"/>
       <c r="Q22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R22"/>
-      <c r="S22"/>
-      <c r="T22"/>
-      <c r="U22"/>
-      <c r="V22"/>
-      <c r="W22"/>
-      <c r="X22" s="19"/>
+      <c r="R22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="16"/>
       <c r="Y22" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Z22"/>
+        <v>1500</v>
+      </c>
       <c r="AA22" s="3">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="AB22" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC22" s="15" t="b">
+        <v>250</v>
+      </c>
+      <c r="AC22" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>155</v>
       </c>
       <c r="AE22" s="3" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG22"/>
+        <v>1.25</v>
+      </c>
       <c r="AH22" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AK22" s="3">
-        <v>8</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="AM22"/>
-      <c r="AN22"/>
-      <c r="AO22" s="3">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>2.5</v>
       </c>
       <c r="AP22" s="3">
-        <v>12</v>
-      </c>
-      <c r="AQ22"/>
-      <c r="AR22"/>
-      <c r="AS22"/>
-      <c r="AT22"/>
-      <c r="AU22"/>
-      <c r="AV22"/>
-      <c r="AW22"/>
-      <c r="AX22"/>
-      <c r="AY22"/>
-      <c r="AZ22"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A23"/>
       <c r="B23" s="3">
-        <v>9101</v>
-      </c>
-      <c r="C23" s="20" t="s">
+        <v>9002</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="H23"/>
-      <c r="I23" t="s">
-        <v>208</v>
-      </c>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
-      <c r="P23"/>
       <c r="Q23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R23"/>
-      <c r="S23"/>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23"/>
-      <c r="W23"/>
-      <c r="X23" s="19"/>
+      <c r="X23" s="16"/>
       <c r="Y23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Z23"/>
+        <v>4000</v>
+      </c>
       <c r="AA23" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AB23" s="3">
-        <v>350</v>
-      </c>
-      <c r="AC23" s="15" t="b">
+        <v>300</v>
+      </c>
+      <c r="AC23" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD23" s="3" t="s">
@@ -3652,230 +3187,152 @@
       <c r="AF23" s="3">
         <v>0</v>
       </c>
-      <c r="AG23" t="s">
-        <v>157</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>158</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AJ23" s="3" t="b">
-        <v>1</v>
-      </c>
       <c r="AK23" s="3">
+        <v>8</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="AO23" s="3">
         <v>12</v>
       </c>
-      <c r="AL23">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>15</v>
-      </c>
       <c r="AP23" s="3">
-        <v>30</v>
-      </c>
-      <c r="AQ23">
-        <v>5</v>
-      </c>
-      <c r="AR23">
-        <v>90</v>
-      </c>
-      <c r="AS23"/>
-      <c r="AT23"/>
-      <c r="AU23"/>
-      <c r="AV23"/>
-      <c r="AW23"/>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A24"/>
       <c r="B24" s="3">
-        <v>9102</v>
-      </c>
-      <c r="C24" s="20" t="s">
+        <v>9101</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="I24" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="I24" t="s">
-        <v>212</v>
-      </c>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-      <c r="P24"/>
       <c r="Q24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R24"/>
-      <c r="S24"/>
-      <c r="T24"/>
-      <c r="U24"/>
-      <c r="V24"/>
-      <c r="W24"/>
-      <c r="X24" s="19"/>
+      <c r="X24" s="16"/>
       <c r="Y24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="Z24"/>
+        <v>2500</v>
+      </c>
       <c r="AA24" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="AB24" s="3">
-        <v>700</v>
-      </c>
-      <c r="AC24" s="15" t="b">
+        <v>350</v>
+      </c>
+      <c r="AC24" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
       <c r="AG24" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AH24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>163</v>
       </c>
+      <c r="AJ24" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="AK24" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AL24">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>15</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>30</v>
+      </c>
+      <c r="AQ24">
         <v>5</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="3">
-        <v>20</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
       <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>1500</v>
-      </c>
-      <c r="AV24"/>
-      <c r="AW24"/>
+        <v>90</v>
+      </c>
       <c r="AX24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A25"/>
       <c r="B25" s="3">
-        <v>9103</v>
-      </c>
-      <c r="C25" s="3" t="s">
+        <v>9102</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="I25" t="s">
         <v>213</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I25" t="s">
-        <v>208</v>
-      </c>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-      <c r="P25"/>
       <c r="Q25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R25"/>
-      <c r="S25"/>
-      <c r="T25"/>
-      <c r="U25"/>
-      <c r="V25"/>
-      <c r="W25"/>
-      <c r="X25" s="19">
-        <v>14</v>
-      </c>
+      <c r="X25" s="16"/>
       <c r="Y25" s="3">
-        <v>14000</v>
-      </c>
-      <c r="Z25"/>
+        <v>9000</v>
+      </c>
       <c r="AA25" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB25" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC25" s="15" t="b">
+        <v>700</v>
+      </c>
+      <c r="AC25" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD25" s="3" t="s">
         <v>155</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="AF25" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="s">
         <v>161</v>
@@ -3884,87 +3341,83 @@
         <v>162</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AK25" s="3">
-        <v>8</v>
-      </c>
-      <c r="AL25"/>
+        <v>22</v>
+      </c>
+      <c r="AL25">
+        <v>5</v>
+      </c>
       <c r="AM25" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AN25" s="3">
-        <v>24</v>
-      </c>
-      <c r="AO25"/>
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
       <c r="AP25" s="3">
-        <v>24</v>
-      </c>
-      <c r="AQ25"/>
-      <c r="AR25"/>
+        <v>20</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
       <c r="AS25">
         <v>0</v>
       </c>
       <c r="AT25">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AU25">
-        <v>2000</v>
-      </c>
-      <c r="AV25"/>
-      <c r="AW25"/>
-      <c r="AX25"/>
-      <c r="AY25"/>
-      <c r="AZ25"/>
+        <v>1500</v>
+      </c>
+      <c r="AX25">
+        <v>20</v>
+      </c>
+      <c r="AY25">
+        <v>15</v>
+      </c>
+      <c r="AZ25">
+        <v>30</v>
+      </c>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A26"/>
       <c r="B26" s="3">
-        <v>9104</v>
-      </c>
-      <c r="C26" s="20" t="s">
+        <v>9103</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H26" t="s">
         <v>216</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="H26" s="17"/>
       <c r="I26" t="s">
-        <v>208</v>
-      </c>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
+        <v>209</v>
+      </c>
       <c r="Q26" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R26"/>
-      <c r="S26"/>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
-      <c r="X26" s="19"/>
+      <c r="X26" s="16">
+        <v>14</v>
+      </c>
       <c r="Y26" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Z26"/>
+        <v>14000</v>
+      </c>
       <c r="AA26" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB26" s="3">
-        <v>350</v>
-      </c>
-      <c r="AC26" s="15" t="b">
+        <v>800</v>
+      </c>
+      <c r="AC26" s="3" t="b">
         <v>1</v>
       </c>
       <c r="AD26" s="3" t="s">
@@ -3974,312 +3427,232 @@
         <v>156</v>
       </c>
       <c r="AF26" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>8</v>
+      </c>
+      <c r="AM26" s="3">
+        <v>8</v>
+      </c>
+      <c r="AN26" s="3">
+        <v>24</v>
+      </c>
+      <c r="AP26" s="3">
+        <v>24</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>400</v>
+      </c>
+      <c r="AU26">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>9104</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>350</v>
+      </c>
+      <c r="AC27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="s">
         <v>157</v>
       </c>
-      <c r="AH26" s="3" t="s">
+      <c r="AH27" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AI27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AJ26" s="3" t="b">
+      <c r="AJ27" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AK27" s="3">
         <v>30</v>
       </c>
-      <c r="AL26">
+      <c r="AL27">
         <v>10</v>
       </c>
-      <c r="AM26"/>
-      <c r="AN26"/>
-      <c r="AO26">
+      <c r="AO27">
         <v>12</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AP27" s="3">
         <v>30</v>
       </c>
-      <c r="AQ26">
+      <c r="AQ27">
         <v>1</v>
       </c>
-      <c r="AR26">
+      <c r="AR27">
         <v>90</v>
       </c>
-      <c r="AS26"/>
-      <c r="AT26"/>
-      <c r="AU26"/>
-      <c r="AW26"/>
-      <c r="AX26"/>
-      <c r="AY26"/>
-      <c r="AZ26"/>
     </row>
-    <row r="27" spans="1:52" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23"/>
-      <c r="B27" s="27">
+    <row r="28" spans="1:52" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="19"/>
+      <c r="B28" s="22">
         <v>9105</v>
       </c>
-      <c r="C27" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="H27" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="24" t="s">
+      <c r="C28" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="H28" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="R27" s="30"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="31">
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="25">
         <v>10000</v>
       </c>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31">
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25">
         <v>1000</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB28" s="25">
         <v>1000</v>
       </c>
-      <c r="AC27" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="31" t="s">
+      <c r="AC28" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="AE27" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF27" s="31">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="31" t="s">
+      <c r="AE28" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF28" s="25">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="AH27" s="31" t="s">
+      <c r="AH28" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="AI27" s="31" t="s">
+      <c r="AI28" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="AK27" s="31">
+      <c r="AK28" s="25">
         <v>100</v>
       </c>
-      <c r="AL27" s="31">
+      <c r="AL28" s="25">
         <v>15</v>
       </c>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="31"/>
-      <c r="AO27" s="31"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="31"/>
-      <c r="AR27" s="31"/>
-      <c r="AS27" s="31">
-        <v>0</v>
-      </c>
-      <c r="AT27" s="31">
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="25"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="25"/>
+      <c r="AQ28" s="25"/>
+      <c r="AR28" s="25"/>
+      <c r="AS28" s="25">
+        <v>0</v>
+      </c>
+      <c r="AT28" s="25">
         <v>1000</v>
       </c>
-      <c r="AU27" s="31">
+      <c r="AU28" s="25">
         <v>2000</v>
       </c>
-      <c r="AV27"/>
-      <c r="AW27" s="31"/>
-      <c r="AX27" s="31"/>
-      <c r="AY27" s="31"/>
-      <c r="AZ27" s="31"/>
-    </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A28"/>
-      <c r="B28" s="19">
-        <v>2001</v>
-      </c>
-      <c r="C28" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" t="s">
-        <v>220</v>
-      </c>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28" t="s">
-        <v>221</v>
-      </c>
-      <c r="I28" t="s">
-        <v>222</v>
-      </c>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="R28" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28"/>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28"/>
-      <c r="X28" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="21">
-        <v>600</v>
-      </c>
-      <c r="Z28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="21">
-        <v>400</v>
-      </c>
-      <c r="AB28" s="21">
-        <v>500</v>
-      </c>
-      <c r="AC28" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE28" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF28" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG28" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH28" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI28" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ28" s="21"/>
-      <c r="AK28" s="21">
-        <v>50</v>
-      </c>
-      <c r="AL28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="21">
-        <v>10</v>
-      </c>
-      <c r="AN28" s="21">
-        <v>10</v>
-      </c>
-      <c r="AO28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="21">
-        <v>8</v>
-      </c>
-      <c r="AQ28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="21">
-        <v>600</v>
-      </c>
-      <c r="AV28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AW28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AX28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AY28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AZ28" s="21">
-        <v>0</v>
-      </c>
+      <c r="AW28" s="25"/>
+      <c r="AX28" s="25"/>
+      <c r="AY28" s="25"/>
+      <c r="AZ28" s="25"/>
     </row>
     <row r="29" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A29"/>
-      <c r="B29" s="19">
-        <v>2002</v>
+      <c r="B29" s="16">
+        <v>2001</v>
       </c>
       <c r="C29" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29" t="s">
         <v>224</v>
       </c>
-      <c r="D29" t="s">
+      <c r="H29" t="s">
         <v>225</v>
       </c>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>226</v>
       </c>
-      <c r="I29" t="s">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
         <v>227</v>
-      </c>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29" t="s">
-        <v>223</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R29" s="18" t="b">
-        <v>0</v>
+      <c r="R29" t="b">
+        <v>1</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4287,101 +3660,98 @@
       <c r="T29">
         <v>0</v>
       </c>
-      <c r="U29"/>
       <c r="V29">
         <v>0</v>
       </c>
-      <c r="W29"/>
-      <c r="X29" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="21">
-        <v>2500</v>
-      </c>
-      <c r="Z29" s="21">
+      <c r="X29" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="18">
+        <v>600</v>
+      </c>
+      <c r="Z29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="18">
+        <v>400</v>
+      </c>
+      <c r="AB29" s="18">
+        <v>500</v>
+      </c>
+      <c r="AC29" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE29" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF29" s="18">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH29" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI29" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18">
+        <v>50</v>
+      </c>
+      <c r="AL29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="18">
         <v>10</v>
       </c>
-      <c r="AA29" s="21">
-        <v>1200</v>
-      </c>
-      <c r="AB29" s="21">
-        <v>1500</v>
-      </c>
-      <c r="AC29" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD29" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE29" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF29" s="21">
-        <v>6</v>
-      </c>
-      <c r="AG29" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH29" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI29" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="21">
-        <v>100</v>
-      </c>
-      <c r="AL29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="21">
-        <v>18</v>
-      </c>
-      <c r="AN29" s="21">
-        <v>12</v>
-      </c>
-      <c r="AO29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="21">
-        <v>12</v>
-      </c>
-      <c r="AQ29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="21">
-        <v>1000</v>
-      </c>
-      <c r="AV29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AW29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AX29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AY29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AZ29" s="21">
+      <c r="AN29" s="18">
+        <v>10</v>
+      </c>
+      <c r="AO29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="18">
+        <v>10</v>
+      </c>
+      <c r="AQ29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="18">
+        <v>600</v>
+      </c>
+      <c r="AV29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AX29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AY29" s="18">
+        <v>0</v>
+      </c>
+      <c r="AZ29" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A30"/>
-      <c r="B30">
-        <v>2003</v>
+      <c r="B30" s="16">
+        <v>2002</v>
       </c>
       <c r="C30" t="s">
         <v>228</v>
@@ -4389,27 +3759,19 @@
       <c r="D30" t="s">
         <v>229</v>
       </c>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
       <c r="H30" t="s">
         <v>230</v>
       </c>
       <c r="I30" t="s">
-        <v>222</v>
-      </c>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
+        <v>231</v>
+      </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q30" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q30" s="3" t="s">
         <v>154</v>
       </c>
       <c r="R30" t="b">
@@ -4421,92 +3783,213 @@
       <c r="T30">
         <v>0</v>
       </c>
-      <c r="U30"/>
       <c r="V30">
         <v>0</v>
       </c>
-      <c r="W30"/>
-      <c r="X30" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="21">
+      <c r="X30" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="18">
+        <v>2500</v>
+      </c>
+      <c r="Z30" s="18">
+        <v>10</v>
+      </c>
+      <c r="AA30" s="18">
+        <v>1200</v>
+      </c>
+      <c r="AB30" s="18">
+        <v>1500</v>
+      </c>
+      <c r="AC30" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE30" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF30" s="18">
+        <v>6</v>
+      </c>
+      <c r="AG30" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH30" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI30" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18">
+        <v>100</v>
+      </c>
+      <c r="AL30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="18">
+        <v>18</v>
+      </c>
+      <c r="AN30" s="18">
+        <v>12</v>
+      </c>
+      <c r="AO30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="18">
+        <v>12</v>
+      </c>
+      <c r="AQ30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="18">
+        <v>1000</v>
+      </c>
+      <c r="AV30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="18">
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>2003</v>
+      </c>
+      <c r="C31" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" t="s">
+        <v>234</v>
+      </c>
+      <c r="I31" t="s">
+        <v>226</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>154</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="X31" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="18">
         <v>4000</v>
       </c>
-      <c r="Z30" s="21">
+      <c r="Z31" s="18">
         <v>15</v>
       </c>
-      <c r="AA30" s="21">
+      <c r="AA31" s="18">
         <v>400</v>
       </c>
-      <c r="AB30" s="21">
+      <c r="AB31" s="18">
         <v>1000</v>
       </c>
-      <c r="AC30" s="21" t="b">
+      <c r="AC31" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AD30" s="21"/>
-      <c r="AE30" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="21" t="s">
+      <c r="AD31" s="18"/>
+      <c r="AE31" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="AH30" s="21" t="s">
+      <c r="AH31" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="AI30" s="21" t="s">
+      <c r="AI31" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="AJ30" s="21"/>
-      <c r="AK30" s="21">
+      <c r="AJ31" s="18"/>
+      <c r="AK31" s="18">
         <v>30</v>
       </c>
-      <c r="AL30" s="21">
+      <c r="AL31" s="18">
         <v>5</v>
       </c>
-      <c r="AM30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="21">
-        <v>5</v>
-      </c>
-      <c r="AQ30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT30" s="21">
+      <c r="AM31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="18">
+        <v>10</v>
+      </c>
+      <c r="AQ31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT31" s="18">
         <v>250</v>
       </c>
-      <c r="AU30" s="21">
+      <c r="AU31" s="18">
         <v>1000</v>
       </c>
-      <c r="AV30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AW30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AX30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AY30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="21">
+      <c r="AV31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AW31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AX31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AY31" s="18">
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="18">
         <v>0</v>
       </c>
     </row>

--- a/Development/Common/GameData/Skill.xlsx
+++ b/Development/Common/GameData/Skill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C0BA2-6F5B-4D88-9FE1-9CDB62C0CAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B303229C-2832-4D6F-8BC1-BEFF13B08610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -771,6 +771,7 @@
       <sz val="11"/>
       <color rgb="FF0A0A0A"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2315,7 +2316,7 @@
       <c r="W11" s="19"/>
       <c r="X11" s="22"/>
       <c r="Y11" s="20">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Z11" s="20">
         <v>30</v>
@@ -2413,7 +2414,7 @@
       </c>
       <c r="X12" s="16"/>
       <c r="Y12" s="3">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="Z12" s="3">
         <v>30</v>
@@ -3601,7 +3602,7 @@
         <v>163</v>
       </c>
       <c r="AK28" s="25">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AL28" s="25">
         <v>15</v>
@@ -3790,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="18">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="Z30" s="18">
         <v>10</v>
@@ -3913,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="Y31" s="18">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="Z31" s="18">
         <v>15</v>
